--- a/results/Int Task Remove ACC 0.4/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.0001322751322751392 +/- 0.0011335943679173074</t>
+          <t>0.005643738977072266 +/- 0.001499118165784819</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.01798941798941801 +/- 0.0019500303692677233</t>
+          <t>-0.00317460317460323 +/- 0.0016236289805574905</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.001102292768959412 +/- 0.0016527041282179016</t>
+          <t>0.007054673721340332 +/- 0.0019520232470175043</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.818342151677428e-05 +/- 0.0009619675586098545</t>
+          <t>0.0035714285714285366 +/- 0.0007997511969672557</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.002469135802469158 +/- 0.0019036184431149104</t>
+          <t>0.0010582010582010138 +/- 0.002125568041127686</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.00039682539682541764 +/- 0.001254097235743205</t>
+          <t>0.012566137566137503 +/- 0.0019445394242680767</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.00035273368606701937 +/- 0.00043200877297764413</t>
+          <t>0.00022045855379188017 +/- 0.00029577618749996286</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.009964726631393283 +/- 0.0018727302100172308</t>
+          <t>0.008068783068783026 +/- 0.0018815333592021215</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.021075837742504388 +/- 0.004577050889721676</t>
+          <t>0.014726631393298006 +/- 0.004637810861483123</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.01252204585537916 +/- 0.003247257961114979</t>
+          <t>0.014858906525573146 +/- 0.005521331554447</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.0016754850088183336 +/- 0.002515933442272864</t>
+          <t>0.00709876543209873 +/- 0.001875323661211362</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.002160493827160459 +/- 0.0012847268328336414</t>
+          <t>0.008421516754850023 +/- 0.002402492544237264</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.00030864197530865444 +/- 0.0016853187701601825</t>
+          <t>0.00996472663139324 +/- 0.001944039478399332</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.00943562610229275 +/- 0.0018518518518518597</t>
+          <t>0.01009700176366839 +/- 0.001678383272546228</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.012433862433862453 +/- 0.002372773200542072</t>
+          <t>-0.0017636684303351524 +/- 0.003392483961494077</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.008641975308641947 +/- 0.0015921931292123162</t>
+          <t>0.004276895943562564 +/- 0.0014496721536837519</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0017195767195766875 +/- 0.0011740323594086656</t>
+          <t>0.0020723104056436957 +/- 0.0016503498476378282</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-0.000749559082892437 +/- 0.0016266196424776802</t>
+          <t>0.005291005291005224 +/- 0.0018392110771264715</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.006261022927689574 +/- 0.0014991181657848336</t>
+          <t>0.0020282186948853086 +/- 0.0011531478686615405</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.0008377425044091447 +/- 0.0001322751322751281</t>
+          <t>0.0002645502645502562 +/- 0.0002924713219008197</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.0032627865961199045 +/- 0.001903618443114899</t>
+          <t>0.003791887125220417 +/- 0.0016870481895687069</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.0032627865961199487 +/- 0.002152831678259914</t>
+          <t>0.004938271604938227 +/- 0.0008549699924896256</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.0027777777777778013 +/- 0.001200234355274796</t>
+          <t>0.0011022927689593788 +/- 0.0011707158771915092</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.007583774250440945 +/- 0.00122825293449596</t>
+          <t>0.0008818342151674985 +/- 0.0009036111786560588</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0060846560846561145 +/- 0.001989508672430068</t>
+          <t>-0.003218694885361595 +/- 0.001436199071860899</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0007936507936507908 +/- 0.0003843826228872031</t>
+          <t>0.001234567901234529 +/- 0.0007837913948249831</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.01843033509700177 +/- 0.0013915109204637975</t>
+          <t>-0.008156966490299877 +/- 0.0025347940655740687</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.003130511463844832 +/- 0.004033608408876314</t>
+          <t>0.005335097001763623 +/- 0.0024105708876255216</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.0006613756613756183 +/- 0.0011707158771915177</t>
+          <t>0.0035273368606701496 +/- 0.0013227513227513255</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.0015432098765432501 +/- 0.0016408989476127233</t>
+          <t>0.010493827160493773 +/- 0.0014860934344226376</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.0003086419753086433 +/- 0.0005235600567477086</t>
+          <t>-0.0005291005291006012 +/- 0.00038438262288720303</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00035273368606700826 +/- 0.0008549699924896254</t>
+          <t>0.0011463844797177769 +/- 0.0006887345393215528</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.0010141093474427044 +/- 0.0012002343552748062</t>
+          <t>0.008156966490299766 +/- 0.0017553817669659982</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.005423280423280452 +/- 0.0031055717200953025</t>
+          <t>0.00467372134038796 +/- 0.0018093725333935943</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.0001322751322751281 +/- 0.00020205360207035695</t>
+          <t>4.409171075837603e-05 +/- 0.00013227513227512808</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.00030864197530863227 +/- 0.0004850088183421364</t>
+          <t>4.409171075833163e-05 +/- 0.0005007855684127498</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.005467372134038817 +/- 0.0012026615253074022</t>
+          <t>-0.004673721340388059 +/- 0.0013109408066418328</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.005599647266313945 +/- 0.0018397395101433097</t>
+          <t>0.003350970017636623 +/- 0.0015799358789390532</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.409171075837603e-05 +/- 0.0005731922398588884</t>
+          <t>-0.00026455026455031173 +/- 0.00040410720414076236</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.0011904761904761641 +/- 0.0010443315063780258</t>
+          <t>-0.0029100529100529516 +/- 0.0012502157741408968</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.0015873015873015927 +/- 0.0013256875113203648</t>
+          <t>0.004365079365079305 +/- 0.0012066959597358004</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-0.0002204585537918913 +/- 0.0008423709512584947</t>
+          <t>0.0020282186948853086 +/- 0.0009079038925032526</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-0.0012786596119929827 +/- 0.0006374264680247574</t>
+          <t>-0.0017195767195767764 +/- 0.0007495590828923926</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.010626102292768991 +/- 0.0015952427262015418</t>
+          <t>-0.006261022927689641 +/- 0.0015501230891752254</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.0007054673721340499 +/- 0.0010283865775741433</t>
+          <t>0.003924162257495534 +/- 0.001157354916085254</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.0008818342151675651 +/- 0.0013373678031837004</t>
+          <t>0.0018959435626101806 +/- 0.0016853187701601768</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.0014550264550264869 +/- 0.0004850088183421757</t>
+          <t>0.0003086419753085989 +/- 0.0006251078870704711</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.001322751322751292 +/- 0.0011154418554385685</t>
+          <t>0.00017636684303347084 +/- 0.0020224594252521346</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.003880070546737191 +/- 0.0015501230891752135</t>
+          <t>0.0054673721340387504 +/- 0.0010283865775741116</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-0.004144620811287502 +/- 0.0014650130269696767</t>
+          <t>0.0011463844797177547 +/- 0.0015675827896500043</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0033950617283950322 +/- 0.0015023567052381628</t>
+          <t>0.011419753086419715 +/- 0.002043973013491923</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.00035273368606700826 +/- 0.0004320087729776192</t>
+          <t>0.003350970017636645 +/- 0.0004909845117134342</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.0006613756613756405 +/- 0.0006901444374999133</t>
+          <t>0.0027777777777777345 +/- 0.0013234859805823331</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>-0.0003968253968253843 +/- 0.0001322751322751281</t>
+          <t>0.0017636684303350414 +/- 0.00027886046385963665</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.0007495590828924037 +/- 0.0017082337414294972</t>
+          <t>0.0017636684303350635 +/- 0.0013373678031836894</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.00286596119929452 +/- 0.0017664220126993183</t>
+          <t>0.0028659611992944865 +/- 0.0011872056453118391</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.0007495590828923926 +/- 0.0004850088183421364</t>
+          <t>0.0011022927689594009 +/- 0.0006613756613756406</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.0003968253968253843 +/- 0.0014550264550264494</t>
+          <t>0.0035714285714285145 +/- 0.0014550264550264578</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-0.0037477954144621074 +/- 0.0021260253000425396</t>
+          <t>-4.409171075843154e-05 +/- 0.001284726832833646</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.0007495590828923926 +/- 0.0003968253968253843</t>
+          <t>0.0014550264550264092 +/- 0.0005931933001355065</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-0.0009259259259259411 +/- 0.0009132414099298169</t>
+          <t>-0.0019400352733686455 +/- 0.0016403064583543662</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.0037477954144620406 +/- 0.00136968470608545</t>
+          <t>0.006437389770723045 +/- 0.002022459425252173</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.006128747795414491 +/- 0.0017904709439371274</t>
+          <t>0.0036155202821869124 +/- 0.0032087134741905165</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-0.005908289241622599 +/- 0.001118922181697477</t>
+          <t>0.0020282186948853086 +/- 0.0009898564515274835</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.00030864197530863227 +/- 0.0004850088183421364</t>
+          <t>0.00044091710758376035 +/- 0.00019718412499997523</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.010097001763668456 +/- 0.0006957554602319072</t>
+          <t>0.0034391534391533863 +/- 0.0014463156496346303</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.00568783068783073 +/- 0.0005731922398588884</t>
+          <t>0.0025573192239858543 +/- 0.0015995023939344856</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.0004850088183421364 +/- 0.0005382079195649611</t>
+          <t>0.00022045855379188017 +/- 0.00029577618749996286</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.005599647266313945 +/- 0.000904686266696805</t>
+          <t>-0.0008377425044092335 +/- 0.0010880919470240761</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.010097001763668467 +/- 0.0011904761904761908</t>
+          <t>0.004365079365079317 +/- 0.0013725204952621875</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.003306878306878325 +/- 0.0008189671790567283</t>
+          <t>0.013095238095238038 +/- 0.001807760141093476</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.00017636684303350413 +/- 0.0004041072041407139</t>
+          <t>-0.00013227513227518362 +/- 0.0003443672696608261</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>-0.0007495590828924259 +/- 0.0007123233871871217</t>
+          <t>0.0005291005291005013 +/- 0.0005849426438016662</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-0.0007495590828924148 +/- 0.0009466891778476236</t>
+          <t>-3.3306690738754695e-17 +/- 0.0003943682499999877</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,52 +1266,52 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-0.00022045855379188017 +/- 0.0003554787366974557</t>
+          <t>0.00017636684303349304 +/- 0.0003527336860670277</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-0.005291005291005302 +/- 0.0011994242071195307</t>
+          <t>0.0027777777777777124 +/- 0.0007649625913976062</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>-4.409171075837603e-05 +/- 0.0001322751322751281</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0005731922398588884 +/- 0.0003968253968253843</t>
+          <t>0.0010141093474426489 +/- 0.0003968253968253843</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0030423280423280573 +/- 0.00177957990040658</t>
+          <t>0.0014991181657847963 +/- 0.0014382280802733571</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>-0.0018959435626102583 +/- 0.0011839260654406953</t>
+          <t>0.003306878306878258 +/- 0.0014919686345404408</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.000837742504409178 +/- 0.0005731922398589251</t>
+          <t>-0.00017636684303354855 +/- 0.0003527336860670555</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.0059523809523809755 +/- 0.0014523517717813647</t>
+          <t>-0.001366843033509746 +/- 0.001284726832833626</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-0.004100529100529116 +/- 0.001308714469105475</t>
+          <t>0.003086419753086378 +/- 0.0010618690104755237</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>-0.003615520282186968 +/- 0.0011119506360598257</t>
+          <t>0.004717813051146336 +/- 0.0010255470325937297</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.009982014388489235 +/- 0.0013308137218478791</t>
+          <t>-0.018030575539568328 +/- 0.002216047037833033</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.01362410071942447 +/- 0.0015839851577165974</t>
+          <t>-0.03313848920863309 +/- 0.003328856837927986</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.001753597122302164 +/- 0.0016514719129682373</t>
+          <t>-0.01812050359712226 +/- 0.002001278155060043</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.00044964028776981466 +/- 0.0013931594770530225</t>
+          <t>0.0003597122302158473 +/- 0.0011516410498979932</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.011735611510791378 +/- 0.0016391840048163725</t>
+          <t>-0.02221223021582732 +/- 0.0017782122242162928</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.005260791366906459 +/- 0.0027354246716286127</t>
+          <t>-0.010161870503597115 +/- 0.0020128623458273054</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.00022482014388487405 +/- 0.0003016278746627271</t>
+          <t>4.496402877698369e-05 +/- 0.00013489208633095105</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.006384892086330929 +/- 0.0015154945635209164</t>
+          <t>-0.003237410071942437 +/- 0.0008483795982065462</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.06564748201438846 +/- 0.0036083457999530467</t>
+          <t>0.03866906474820144 +/- 0.004169792488981894</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.06582733812949638 +/- 0.004876887360775633</t>
+          <t>0.04316546762589929 +/- 0.0036969073365277884</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.004316546762589901 +/- 0.0019203378151135461</t>
+          <t>-0.0017985611510791034 +/- 0.0020407923953075975</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.006205035971223028 +/- 0.0021356730372370475</t>
+          <t>-0.03453237410071939 +/- 0.0020388100807112483</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-0.011285971223021607 +/- 0.002243249943033522</t>
+          <t>-0.006339928057553945 +/- 0.002482812534582439</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.046043165467625866 +/- 0.0026001496933095243</t>
+          <t>0.021537769784172676 +/- 0.002243249943033517</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.01874999999999999 +/- 0.003847250108027375</t>
+          <t>0.008318345323741016 +/- 0.002677153893274141</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.0025629496402877817 +/- 0.0013346063021273304</t>
+          <t>-0.0022931654676258684 +/- 0.0011802522255761427</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.00732913669064752 +/- 0.0009861381384649718</t>
+          <t>-0.011151079136690634 +/- 0.001773658536269435</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.0009442446043165242 +/- 0.0019748373431652724</t>
+          <t>-0.011016187050359704 +/- 0.0020233812949640405</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.0066097122302158475 +/- 0.0010458366321594492</t>
+          <t>-0.017580935251798536 +/- 0.0013704811739323746</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-3.3306690738754695e-17 +/- 0.00034828986926325475</t>
+          <t>0.0008093525179856287 +/- 0.00048427741071352534</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.0007643884892086117 +/- 0.0022843319776763567</t>
+          <t>0.005395683453237432 +/- 0.0024297223176450123</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.0029676258992805795 +/- 0.0009037657932662604</t>
+          <t>0.005845323741007202 +/- 0.0018097672479764427</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.008273381294964011 +/- 0.0018231236450281757</t>
+          <t>-0.001618705035971213 +/- 0.001321667127401006</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.002922661870503551 +/- 0.0014946735736146544</t>
+          <t>0.0017985611510791476 +/- 0.0013338486487582007</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.004046762589928032 +/- 0.0011551468146281734</t>
+          <t>0.0006744604316546998 +/- 0.0013822325673506484</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0009442446043165132 +/- 0.00031474820143884293</t>
+          <t>0.0006744604316547109 +/- 0.0003016278746627271</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.0020683453237409833 +/- 0.0027586082104636505</t>
+          <t>-0.016861510791366885 +/- 0.0014673713014460895</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.008003597122302142 +/- 0.0019371096428541276</t>
+          <t>-0.0003597122302157918 +/- 0.0018186824115248852</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.000719424460431628 +/- 0.0009685548214270641</t>
+          <t>0.007553956834532393 +/- 0.0015935292398083856</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.011510791366906447 +/- 0.001800807949145761</t>
+          <t>0.003012589928057563 +/- 0.0016830006539759663</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-8.992805755397848e-05 +/- 0.0005616005394243094</t>
+          <t>0.00022482014388491844 +/- 0.00022482014388491842</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.001214028776978382 +/- 0.0006374751294405555</t>
+          <t>0.00044964028776981466 +/- 0.0005687549748504332</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,272 +1491,272 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.0006294964028776828 +/- 0.0016236933529916956</t>
+          <t>-0.001978417266187027 +/- 0.001909780627841296</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.003102517985611497 +/- 0.0013101440903177726</t>
+          <t>0.0008543165467626013 +/- 0.0012305694409536052</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-0.0006744604316546998 +/- 0.0007319613577382966</t>
+          <t>0.0003147482014388747 +/- 0.000570529565667706</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.0010341726618705248 +/- 0.0008543165467626007</t>
+          <t>0.0010791366906474976 +/- 0.0010866048537405179</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.00022482014388491844 +/- 0.0016243158154845658</t>
+          <t>0.00022482014388491844 +/- 0.0013224317598788213</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.0023830935251798356 +/- 0.001240387969796215</t>
+          <t>0.0024730215827338366 +/- 0.001243643586865045</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.00013489208633091777 +/- 0.0005339182593092551</t>
+          <t>-0.0003147482014388414 +/- 0.0005705295656676894</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.0022482014388488848 +/- 0.0018647878914863105</t>
+          <t>0.0027877697841726667 +/- 0.0008947728750958623</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0017985611510791034 +/- 0.00146392271547659</t>
+          <t>0.00026978417266189104 +/- 0.001209858277614534</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-0.00022482014388491844 +/- 0.0010496958210367625</t>
+          <t>0.0019784172661870604 +/- 0.001086604853740527</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.006294964028776972 +/- 0.0021750695364114634</t>
+          <t>0.00705935251798564 +/- 0.0016830006539759951</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>-0.010656474820143902 +/- 0.0019501122699821388</t>
+          <t>-0.018165467625899257 +/- 0.004651984588625031</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.002877697841726601 +/- 0.002176927776422699</t>
+          <t>0.0028327338129496503 +/- 0.0014783527178753235</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.0019334532374100876 +/- 0.0013039568345323612</t>
+          <t>0.001978417266187071 +/- 0.0007577472817604645</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.0005845323741006991 +/- 0.0007800967433856758</t>
+          <t>-0.000944244604316491 +/- 0.0007095204063875626</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.004766187050359694 +/- 0.0017895457501917664</t>
+          <t>0.0013938848920863611 +/- 0.0016268032837343002</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.012589928057553934 +/- 0.0019804600310742403</t>
+          <t>0.003147482014388514 +/- 0.002495402324732302</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.012455035971223027 +/- 0.001991150164162287</t>
+          <t>-0.008767985611510754 +/- 0.0013967827848029729</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0011241007194244257 +/- 0.002852647828338448</t>
+          <t>-0.006609712230215814 +/- 0.0015054558491711348</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.0013938848920862946 +/- 0.0005845323741007093</t>
+          <t>-0.0011241007194244146 +/- 0.0007590801715887552</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>-8.992805755398958e-05 +/- 0.0003364799808249986</t>
+          <t>-0.0008093525179855732 +/- 0.0007194244604316321</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>4.496402877699479e-05 +/- 0.000242138705356773</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>-0.0006744604316546554 +/- 0.0023557890103290974</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-0.005620503597122295 +/- 0.0018013692107922868</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-0.007868705035971247 +/- 0.002880857640223268</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.014838129496402851 +/- 0.0026141082470770684</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>2.2204460492503132e-17 +/- 0.0006965797385265165</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.006205035971223049 +/- 0.002419716555229103</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>-0.003327338129496393 +/- 0.002521195282171987</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.0010791366906474976 +/- 0.00045854492028713113</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.0014388489208633337 +/- 0.0022192378919519795</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.0005845323741007324 +/- 0.0038942587090242176</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-0.012499999999999989 +/- 0.0014047211647314226</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.005260791366906459 +/- 0.0010064311729136403</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-0.0008093525179856287 +/- 0.0002697841726618577</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.0066996402877697704 +/- 0.0017810523669369036</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>-0.0029676258992806016 +/- 0.0021109162939398265</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.00022482014388486293 +/- 0.00036251158940190753</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.002473021582733792 +/- 0.0024483729118816512</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.020233812949640273 +/- 0.001831973811822274</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-0.00179856115107917 +/- 0.0029825762503195956</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.00026978417266183553 +/- 0.0009258660198729302</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.004811151079136699 +/- 0.0011023067151197294</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0.0013938848920863611 +/- 0.0012630010706104308</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>8.992805755396738e-05 +/- 0.0007194244604316419</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.0010791366906474976 +/- 0.0017895457501917351</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.00625 +/- 0.0017923679341721977</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.0056205035971223175 +/- 0.001411182987992389</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>-0.00040467625899275327 +/- 0.00013489208633091777</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.00017985611510794585 +/- 0.0009474508770551008</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.001528776978417301 +/- 0.0007023605823657049</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.009937050359712185 +/- 0.0017466658812549417</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.005215827338129498 +/- 0.001534057743635964</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.005935251798561148 +/- 0.0009809992908844823</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.005035971223021562 +/- 0.0012198435221448362</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.005575539568345311 +/- 0.0011586419718278057</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.005575539568345311 +/- 0.0009258660198729433</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.00017985611510789034 +/- 0.0006099217610724189</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.0005395683453237154 +/- 0.0005243661775939834</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.00017985611510789034 +/- 0.000220277854566804</t>
-        </is>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0011690647482013982 +/- 0.0006099217610724026</t>
+          <t>0.00017985611510795696 +/- 0.00045854492028711156</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.0031474820143884584 +/- 0.0015445651112695844</t>
+          <t>0.004091726618705027 +/- 0.0011629961471562435</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>4.496402877698369e-05 +/- 0.00013489208633095105</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0007643884892086006 +/- 0.0005705295656676885</t>
+          <t>0.0012140287769784376 +/- 0.0005705295656676885</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0030125899280575297 +/- 0.0013938848920863468</t>
+          <t>0.003282374100719421 +/- 0.0007800967433856829</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.003956834532374087 +/- 0.0006907505168946562</t>
+          <t>0.002517985611510809 +/- 0.0020128623458272516</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-0.0003597122302158584 +/- 0.0003919873150665998</t>
+          <t>-0.0010341726618704693 +/- 0.0009004039745728728</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.004946043165467595 +/- 0.0011725184182019121</t>
+          <t>0.003552158273381301 +/- 0.0008155736127345671</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.004316546762589901 +/- 0.0015858985691140893</t>
+          <t>0.00638489208633094 +/- 0.0014332173966285578</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.0017535971223021196 +/- 0.0005845323741007093</t>
+          <t>8.992805755398958e-05 +/- 0.0011516410498979845</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0003733084461035929 +/- 0.0008804462092446663</t>
+          <t>-0.003546430237984133 +/- 0.0013556546006844557</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.007046196920205317 +/- 0.0014068887943706327</t>
+          <t>-0.0050863275781614535 +/- 0.0015539734769338968</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.00013999066728884735 +/- 0.001065115465283558</t>
+          <t>0.0029864675688287433 +/- 0.0013716228144376166</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0021465235650956595 +/- 0.0010265982267848807</t>
+          <t>-0.0002799813345776947 +/- 0.0010265982267848805</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.00018665422305179645 +/- 0.0007581930382301406</t>
+          <t>-0.001166588894073728 +/- 0.0016063382620679887</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.004386374241717217 +/- 0.0023443502915689155</t>
+          <t>-0.0027531497900139977 +/- 0.0028874901548119414</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.666355576294911e-05 +/- 0.00013999066728884733</t>
+          <t>0.0003733084461035929 +/- 0.0004068034478339404</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.0005132991133924402 +/- 0.001437510200723225</t>
+          <t>0.0021931871208586084 +/- 0.001416144741529959</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.019878674755016323 +/- 0.004226595193364161</t>
+          <t>-0.008586094260382638 +/- 0.0034869886499802887</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.006906206252916469 +/- 0.004040104679778508</t>
+          <t>0.004993000466635556 +/- 0.004392575118801196</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.0006066262249183385 +/- 0.0011814268689848025</t>
+          <t>-0.0011199253383107788 +/- 0.0011468227463783949</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.0009332711152589823 +/- 0.0008082364944325135</t>
+          <t>-0.0013532431171255244 +/- 0.0019956514027385055</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.005599626691553894 +/- 0.000978823003425246</t>
+          <t>0.004619692020531962 +/- 0.0013755859050848035</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.016752216518898733 +/- 0.0033484149698385867</t>
+          <t>0.015958936070928596 +/- 0.0020103275061631367</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.016285580961269242 +/- 0.0028571664983372143</t>
+          <t>0.01530564629024731 +/- 0.0022065497746219104</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.001633224451703219 +/- 0.0015927249804830615</t>
+          <t>-0.004806346243583759 +/- 0.0019132057862809137</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.0010732617825478298 +/- 0.0008095824345729102</t>
+          <t>-0.0002799813345776947 +/- 0.0010475942286814577</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>9.332711152589823e-05 +/- 0.002511175743737509</t>
+          <t>-0.0017732151189920665 +/- 0.0014873894027540105</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.0013532431171255244 +/- 0.001567923249315113</t>
+          <t>-0.001633224451703219 +/- 0.000891505981079925</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>4.666355576294911e-05 +/- 0.00025129093827039203</t>
+          <t>0.0002799813345776947 +/- 0.0006329752667405753</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00023331777881474558 +/- 0.0014037899166114156</t>
+          <t>0.0008866075594960332 +/- 0.0024017002767070025</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.0021931871208586084 +/- 0.001958202077308192</t>
+          <t>-0.0005132991133924402 +/- 0.0011324928697630976</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.0014465702286514226 +/- 0.001259916005599626</t>
+          <t>-0.004293047130191319 +/- 0.0013811151271067416</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0010265982267848805 +/- 0.001176810099199112</t>
+          <t>-0.0008399440037330841 +/- 0.0012310691514953722</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.001959869342043863 +/- 0.0005025818765407842</t>
+          <t>-0.0011199253383107788 +/- 0.0008399440037330841</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.00023331777881474558 +/- 0.00031302864827341886</t>
+          <t>-0.00032664489034064383 +/- 0.0003644540212742254</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-0.0026131591227251507 +/- 0.0014637785479568934</t>
+          <t>-0.00685954269715352 +/- 0.0023889735391824916</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.007279514699020062 +/- 0.0016979379746766444</t>
+          <t>-0.005132991133924403 +/- 0.0018312101605551633</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-0.0013065795613625753 +/- 0.0015865608959402698</t>
+          <t>-0.009986000933271112 +/- 0.0014932337844143718</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.0050863275781614535 +/- 0.001763981163923079</t>
+          <t>-0.005179654689687352 +/- 0.0019063647424932793</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-0.0019132057862809137 +/- 0.0006066262249183385</t>
+          <t>0.0005599626691553894 +/- 0.0004068034478339404</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0003614543486894461</t>
+          <t>-4.666355576294911e-05 +/- 0.0004402231046223331</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.001259916005599626 +/- 0.0023980709580083233</t>
+          <t>0.0010732617825478298 +/- 0.0019245534883155645</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.006812879141390571 +/- 0.001710714211836057</t>
+          <t>-0.004713019132057861 +/- 0.0019956514027385055</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.00013999066728884735 +/- 0.00029879254491053876</t>
+          <t>0.0013532431171255244 +/- 0.0005696012886483293</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.0005132991133924402 +/- 0.0005696012886483294</t>
+          <t>0.0018198786747550156 +/- 0.0003876166058291214</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.001633224451703219 +/- 0.0008412392149939308</t>
+          <t>-0.005739617358842741 +/- 0.0016831254126804878</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>-0.005132991133924403 +/- 0.0016431933608641158</t>
+          <t>-0.00317312179188054 +/- 0.0020103275061631363</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.00032664489034064383 +/- 0.0005132991133924403</t>
+          <t>-0.0006999533364442367 +/- 0.00043021672689187506</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.00041997200186654203 +/- 0.0012425130149971387</t>
+          <t>0.00046663555762949116 +/- 0.0015192553052822864</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.004526364909006065 +/- 0.0009799346710219314</t>
+          <t>-0.00527298180121325 +/- 0.0010234116751965143</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.005412972468502098 +/- 0.0006664888874048388</t>
+          <t>-0.00317312179188054 +/- 0.0008028301695793395</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.010872608492767144 +/- 0.0023706739702996794</t>
+          <t>0.0009332711152589823 +/- 0.0019352721748322642</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.0016798880074661681 +/- 0.0020889434704245806</t>
+          <t>-0.004806346243583759 +/- 0.0025732740418034964</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.00013999066728884735 +/- 0.0009344369759449734</t>
+          <t>0.0022398506766215577 +/- 0.0011199253383107788</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.0026598226784880995 +/- 0.0010853666215224454</t>
+          <t>0.001213252449836677 +/- 0.0011081980482536549</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4.666355576294911e-05 +/- 0.00013999066728884733</t>
+          <t>-0.00032664489034064383 +/- 0.00029879254491053876</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.0037330844610359293 +/- 0.0014153757245079883</t>
+          <t>0.006626224918338775 +/- 0.001501957717165756</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.005412972468502098 +/- 0.0011656552493510771</t>
+          <t>0.009379374708352772 +/- 0.001836553304167468</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.016518898740083988 +/- 0.0024354621279887786</t>
+          <t>-0.0006066262249183385 +/- 0.0031720922817279206</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.013859076061595888 +/- 0.0017713721788242928</t>
+          <t>-0.007699486700886604 +/- 0.0021812404839048507</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-0.0006066262249183385 +/- 0.00029879254491053876</t>
+          <t>4.666355576294911e-05 +/- 0.0009437120119531813</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.0005132991133924402 +/- 0.00032664489034064383</t>
+          <t>-0.0011199253383107788 +/- 0.00037330844610359296</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.00032664489034064383 +/- 0.00021383927647950713</t>
+          <t>0.00041997200186654203 +/- 0.0003266448903406438</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-0.009099393373775078 +/- 0.0014495776544105516</t>
+          <t>-0.007046196920205317 +/- 0.0032426974620796416</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.0034064395706952856 +/- 0.001416144741529959</t>
+          <t>-0.0073261782547830116 +/- 0.0021892121522612963</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,147 +2061,147 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.0005132991133924402 +/- 0.0003876166058291214</t>
+          <t>-0.00023331777881474558 +/- 0.0006681204415901234</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.001213252449836677 +/- 0.0009144152096250777</t>
+          <t>0.014279048063462429 +/- 0.001238124046796229</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-0.0016798880074661681 +/- 0.001710714211836057</t>
+          <t>0.002053196453569761 +/- 0.001564447467497919</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.001213252449836677 +/- 0.00030953101169905724</t>
+          <t>-0.0009799346710219314 +/- 0.0005696012886483293</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-0.0007466168922071858 +/- 0.0007863882196151521</t>
+          <t>0.001539897340177321 +/- 0.0007244131916126933</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.008306112925804942 +/- 0.0018874240239063627</t>
+          <t>-0.0017732151189920665 +/- 0.002829212578856577</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.0006532897806812877 +/- 0.0017484828740266156</t>
+          <t>0.00046663555762949116 +/- 0.0017584175157645133</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-9.332711152589823e-05 +/- 0.0010392467312795182</t>
+          <t>-0.0017265515632291172 +/- 0.0011814268689848023</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
+          <t>0.00018665422305179645 +/- 0.00022860380240626943</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>-0.0003733084461035929 +/- 0.0014578160850969018</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>-0.0005132991133924402 +/- 0.001391325386455956</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>-0.0006532897806812877 +/- 0.0004758767628178052</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0.0005132991133924402 +/- 0.0013107393285289903</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0.004013065795613624 +/- 0.0010475942286814577</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>-0.0014932337844143716 +/- 0.0010392467312795182</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>-9.332711152589823e-05 +/- 0.0002799813345776947</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>-0.0006066262249183385 +/- 0.0009799346710219314</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>-0.0005132991133924402 +/- 0.0006066262249183385</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.00032664489034064383 +/- 0.0011439711313234958</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>9.332711152589823e-05 +/- 0.0006532897806812877</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>0.0024731684554363032 +/- 0.0006277939359343773</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>-0.0016798880074661681 +/- 0.0007289080425484508</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0.0025664955669622014 +/- 0.000984368787201539</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>0.0008399440037330841 +/- 0.0009517535256356103</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>0.00018665422305179645 +/- 0.00022860380240626943</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>-0.0006066262249183385 +/- 0.00029879254491053876</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>9.332711152589823e-05 +/- 0.00018665422305179645</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>0.0003733084461035929 +/- 0.0002799813345776947</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>-0.00023331777881474558 +/- 0.0014645221489944199</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>-9.332711152589823e-05 +/- 0.0002799813345776947</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>0.0024731684554363032 +/- 0.0012702433587322625</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.00013999066728884735 +/- 0.00021383927647950716</t>
+          <t>-0.0008866075594960332 +/- 0.00044022310462233315</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>-0.000793280447970135 +/- 0.0006615700830031647</t>
+          <t>-0.0006999533364442367 +/- 0.0012736672014891438</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.0028464769015398962 +/- 0.0010105649942934065</t>
+          <t>0.0002799813345776947 +/- 0.0015077456296223523</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>-0.0002799813345776947 +/- 0.00042767855295901426</t>
+          <t>-0.0009799346710219314 +/- 0.0006415178294385214</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.0022398506766215577 +/- 0.000829509511648678</t>
+          <t>-0.003079794680354642 +/- 0.001592041260777599</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.0028464769015398962 +/- 0.0006415178294385214</t>
+          <t>-0.001259916005599626 +/- 0.0014465702286514226</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.001213252449836677 +/- 0.000698396152454305</t>
+          <t>-0.0019132057862809137 +/- 0.0017884991037551835</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.015341959334565647 +/- 0.0017141623836406143</t>
+          <t>0.0009242144177449618 +/- 0.0015326362247483356</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.019963031423290156 +/- 0.0020541692024854796</t>
+          <t>-0.0030499075785581755 +/- 0.0003065272449496845</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.009288354898336371 +/- 0.0009571310155826035</t>
+          <t>-0.011229205175600688 +/- 0.0014175472874471272</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.007948243992606241 +/- 0.0015298470755311434</t>
+          <t>-0.005961182994454683 +/- 0.0006680606420887701</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.007347504621072143 +/- 0.0013778236151456163</t>
+          <t>-0.0036506469500923846 +/- 0.0012646887415345652</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.010212569316081378 +/- 0.0018069514598906833</t>
+          <t>0.0034195933456562357 +/- 0.0015354203073785614</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>-9.242144177448174e-05 +/- 0.0001848428835489635</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.009796672828096153 +/- 0.001738899050113375</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-0.0018484288354898015 +/- 0.002780334372734082</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.009565619223659939 +/- 0.0025314872319412863</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-0.0030499075785581976 +/- 0.0010778099620786159</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-0.0045286506469500495 +/- 0.001714162383640603</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-0.014463955637707904 +/- 0.0023017392616288997</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>-0.00956561922365986 +/- 0.002167967487197767</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.0022181146025878505 +/- 0.003098531351985258</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>-0.0008780036968576322 +/- 0.0017711430588481267</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.002079482439926095 +/- 0.0016565109361307815</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.004944547134935351 +/- 0.0012234937425946195</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-0.005591497227356712 +/- 0.0017222407720503062</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0020332717190388538 +/- 0.0010974438158075828</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.006561922365988959 +/- 0.003925464063141466</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.006469500924214455 +/- 0.0031409695874244957</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.0004158964879852567 +/- 0.0017950946949681012</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.010720887245840981 +/- 0.0016763731189664416</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.003881700554528711 +/- 0.0015073480989186783</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.0110443622920517 +/- 0.0016846327295340214</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0.003743068391866944 +/- 0.0035761843648698466</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0.007855822550831826 +/- 0.0014613113032201147</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.0036044362292052324 +/- 0.0007099025644980117</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0.008133086876155304 +/- 0.0012604604156178983</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0.00526802218114607 +/- 0.002026960462057415</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.0006931608133087241 +/- 0.00023105360443620437</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0018946395563771202 +/- 0.0015527077279492959</t>
+          <t>-0.002772643253234708 +/- 0.001033303131931509</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0027264325323475558 +/- 0.0015388933276660399</t>
+          <t>0.002726432532347567 +/- 0.0007855822550831876</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.0010628465804065957 +/- 0.0012234937425946234</t>
+          <t>-0.0035120147874306397 +/- 0.0009055414945594107</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.004713493530499035 +/- 0.0010896327285167726</t>
+          <t>0.0015711645101664118 +/- 0.0009954093913372582</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.004066543438077575 +/- 0.0009195817348489745</t>
+          <t>-0.0030036968576709565 +/- 0.002179755344745054</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0016635859519407714 +/- 0.0005145808098733852</t>
+          <t>0.0003234750462107527 +/- 0.00041589648798521475</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.00859519408502769 +/- 0.0012939001848428795</t>
+          <t>-0.011829944547134907 +/- 0.0014787430683918844</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.006007393715342013 +/- 0.003174780783238032</t>
+          <t>0.006792975970425186 +/- 0.001704793599417442</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.0029112754158965417 +/- 0.001883334923504143</t>
+          <t>0.003927911275415941 +/- 0.0018397439221251716</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.00013863216266168932 +/- 0.0018605196062104951</t>
+          <t>0.009981515711645128 +/- 0.002005779520721867</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-0.0005083179297596607 +/- 0.00038385507684462713</t>
+          <t>0.0001848428835490079 +/- 0.0003696857670979742</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.0015711645101663008 +/- 0.0011356936901519923</t>
+          <t>-0.0006931608133086576 +/- 0.00042604179562351845</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.0001848428835490301 +/- 0.0012772897376234077</t>
+          <t>0.0007855822550832281 +/- 0.002216670047174007</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.0062384473197782285 +/- 0.0030320008691911847</t>
+          <t>0.0009242144177449618 +/- 0.0014167938740070392</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-4.621072088720757e-05 +/- 0.0007579121749933607</t>
+          <t>-0.0013863216266173151 +/- 0.0007451254850553006</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.0016173752310535638 +/- 0.0007233121923520437</t>
+          <t>-0.001432532347504567 +/- 0.0009571310155826234</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.0016635859519407935 +/- 0.001016635859519387</t>
+          <t>-0.0049445471349352735 +/- 0.0014024021169587327</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.00489833641404811 +/- 0.001419805128996037</t>
+          <t>-0.0007855822550831504 +/- 0.0015193421647665133</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.00041589648798516786 +/- 0.00038385507684460176</t>
+          <t>9.242144177453726e-05 +/- 0.0008214597428203064</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.0005083179297597385 +/- 0.0009345539933529127</t>
+          <t>-0.0053604436229204855 +/- 0.0017315151566723835</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.005129390018484337 +/- 0.0018765194551060161</t>
+          <t>0.0034195933456562357 +/- 0.0018850349403300437</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.003743068391866944 +/- 0.001346469712045596</t>
+          <t>-0.003142329020332668 +/- 0.0012872817261722945</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.009750462107208835 +/- 0.001746863047267634</t>
+          <t>-0.013031423290203282 +/- 0.001320042223390538</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-0.009242144177449108 +/- 0.002937199368220099</t>
+          <t>-0.0077171903881700366 +/- 0.0020253795749363306</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>9.242144177452616e-05 +/- 0.0009649081801211159</t>
+          <t>-0.00032347504621067503 +/- 0.001257916597857326</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.006515711645101707 +/- 0.0009345539933528803</t>
+          <t>0.0010628465804067067 +/- 0.0014473622701816936</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.00013863216266168932 +/- 0.000548721907903763</t>
+          <t>1.1102230246251566e-17 +/- 0.00046210720887246426</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.0014787430683919078 +/- 0.0016114228996453666</t>
+          <t>-0.002171903881700499 +/- 0.0010547793170529853</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.00965804066543433 +/- 0.0014235602403650039</t>
+          <t>-0.021719038817005522 +/- 0.0012226207537266915</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-0.003789279112754107 +/- 0.0012191225469753012</t>
+          <t>-0.005591497227356712 +/- 0.0011772402220755031</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.008086876155267963 +/- 0.001493829008802654</t>
+          <t>-0.006792975970425075 +/- 0.0018719620240784652</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-0.0001386321626616782 +/- 0.0007746328379962972</t>
+          <t>-0.001524953789279071 +/- 0.0010547793170529848</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>-0.0012939001848428112 +/- 0.0007393715341959387</t>
+          <t>-0.0007393715341958984 +/- 0.00042352825276856</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.0012939001848429332 +/- 0.00040285572491133764</t>
+          <t>-0.004297597042513835 +/- 0.0004158964879852209</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.020887245841035074 +/- 0.0013985901987450698</t>
+          <t>-0.00993530499075781 +/- 0.0014649600262612874</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.012939001848428777 +/- 0.002418900615213014</t>
+          <t>0.0011552680221811995 +/- 0.0017927139317255832</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.000184842883549019 +/- 0.0005917859738847422</t>
+          <t>-0.0010628465804066178 +/- 0.0007465570435029365</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.0057763401109057755 +/- 0.0012094503076064953</t>
+          <t>0.001432532347504667 +/- 0.0020190436483321214</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-0.01945471349353045 +/- 0.0013932359918374505</t>
+          <t>-0.013909426987060946 +/- 0.0019654501218240956</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>-0.0005545286506468905 +/- 0.0006791561209195377</t>
+          <t>-0.001016635859519377 +/- 0.0006469500924214326</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-0.00254158964879847 +/- 0.0007522560349399271</t>
+          <t>0.0044362292051756454 +/- 0.0009055414945594095</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.006146025878003636 +/- 0.0013078532068470572</t>
+          <t>-0.009519408502772619 +/- 0.0012434033315225183</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-0.006746765249537834 +/- 0.0016941130110742684</t>
+          <t>-0.00688539741219959 +/- 0.0017345955988099352</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.005591497227356667 +/- 0.000911417880005372</t>
+          <t>-0.007024029574861312 +/- 0.001049705794048126</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-0.0003696857670979048 +/- 0.0004977046956686069</t>
+          <t>4.621072088725198e-05 +/- 0.00013863216266175591</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.0016173752310536637 +/- 0.0010984162961187314</t>
+          <t>-0.004297597042513823 +/- 0.0020876815153561086</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.007486136783733855 +/- 0.0017632887272032087</t>
+          <t>0.0006007393715342313 +/- 0.001547196769203624</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-0.0043438077634010645 +/- 0.0009055414945593812</t>
+          <t>0.0009242144177449618 +/- 0.0007451254850553351</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.015526802218114555 +/- 0.002189042381206474</t>
+          <t>-0.014140480591497195 +/- 0.0022657394957728907</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-0.007024029574861312 +/- 0.0008719021378980254</t>
+          <t>0.002634011090573052 +/- 0.0015880628722217756</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-0.025924214417744885 +/- 0.001987060998151588</t>
+          <t>-0.012754158964879825 +/- 0.0015629884034461697</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>4.4408920985006264e-17 +/- 0.0004133212527726096</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.00046210720887250866 +/- 0.0009693242589372898</t>
+          <t>-0.0006469500924214166 +/- 0.0008570811918203114</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.0005083179297596385 +/- 0.0009114178800053483</t>
+          <t>4.6210720887285284e-05 +/- 0.0011772402220755105</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,52 +2601,52 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.0053142329020332115 +/- 0.0009299728187383702</t>
+          <t>-0.0008780036968576432 +/- 0.0007579121749933627</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-0.0006469500924214056 +/- 0.0014931140870058565</t>
+          <t>-0.0023567467652494956 +/- 0.0010425613837965189</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.0005545286506470015 +/- 0.0001848428835489635</t>
+          <t>0.0013401109057301964 +/- 0.00013863216266175594</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>-0.0029112754158964306 +/- 0.0010748339509808738</t>
+          <t>-0.0007855822550831615 +/- 0.0007465570435029221</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0009242144177449618 +/- 0.0010738401144752678</t>
+          <t>0.0018022181146026273 +/- 0.0009571310155826341</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.00046210720887249754 +/- 0.0013393139321801794</t>
+          <t>-0.0030499075785582084 +/- 0.0017801626880090831</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>-0.0012476894639555703 +/- 0.000508317929759698</t>
+          <t>0.0029574861367837935 +/- 0.0007508353423877802</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.0030499075785581755 +/- 0.001434766607787436</t>
+          <t>-0.00027726432532345637 +/- 0.0011726966303557765</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.007717190388170025 +/- 0.0011138605169310565</t>
+          <t>0.01030499075785587 +/- 0.0017783624218940589</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.0023105360443622324 +/- 0.001033303131931519</t>
+          <t>0.0005545286506469904 +/- 0.0016763731189664878</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.0022086466165413985 +/- 0.0011710465972158838</t>
+          <t>0.0009398496240601517 +/- 0.0009398496240601462</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,432 +2666,432 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0015977443609022312 +/- 0.0012988980226583942</t>
+          <t>-0.00413533834586467 +/- 0.0010674639747744923</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.00634398496240598 +/- 0.0022949465126080363</t>
+          <t>0.002913533834586468 +/- 0.001342373764763702</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.0015507518796992747 +/- 0.0010089713606007415</t>
+          <t>0.0009868421052631638 +/- 0.0016339603995031648</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.005122180451127845 +/- 0.0014168057736542524</t>
+          <t>-0.0010808270676691766 +/- 0.001152034837606322</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.00046992481203009804 +/- 0.0009398496240601628</t>
+          <t>-0.00046992481203007587 +/- 0.0018441181269124596</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.699248120300092e-05 +/- 0.00014097744360900275</t>
+          <t>0.0001409774436090361 +/- 0.00021534660220659207</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.0012687969924812248 +/- 0.002143702016533274</t>
+          <t>-0.003618421052631593 +/- 0.001573371150637508</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.025140977443609012 +/- 0.003403306965883444</t>
+          <t>0.025516917293233077 +/- 0.004296922176915858</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.017716165413533814 +/- 0.004053629283497119</t>
+          <t>0.028853383458646596 +/- 0.0038014564692023943</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.005075187969924844 +/- 0.002328855581459386</t>
+          <t>-0.002772556390977432 +/- 0.0011010690332575255</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-0.0014567669172932507 +/- 0.0010808270676691755</t>
+          <t>-0.0003289473684210509 +/- 0.0010518340829698786</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0036654135338345718 +/- 0.0011472326706516666</t>
+          <t>0.0025845864661654394 +/- 0.0017739272639263975</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.038251879699248134 +/- 0.004498533061569294</t>
+          <t>-0.03637218045112781 +/- 0.004124644409302942</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.031203007518796965 +/- 0.0035115679872686797</t>
+          <t>0.01522556390977443 +/- 0.002497242529245567</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.0009868421052631304 +/- 0.0012687969924812018</t>
+          <t>0.003101503759398516 +/- 0.0017227728176525642</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.0016917293233082553 +/- 0.0013652104366855137</t>
+          <t>0.0018327067669173026 +/- 0.0011010690332575114</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.0037593984962405957 +/- 0.0018078368479014454</t>
+          <t>0.00046992481203006475 +/- 0.0016680676080168128</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.002772556390977432 +/- 0.000926836603539294</t>
+          <t>-0.000375939849624074 +/- 0.001437693471877667</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>-9.398496240602406e-05 +/- 0.0003516595288321711</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.003853383458646631 +/- 0.003072891489524772</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-0.0030075187969924922 +/- 0.0012468514249456373</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.0009868421052631638 +/- 0.0015649272373446054</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0009868421052631527 +/- 0.00085236640729403</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-0.003148496240601506 +/- 0.0020915613801003757</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.000375939849624074 +/- 0.000548021794628338</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.006437969924812015 +/- 0.0028042347270367737</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>-0.007330827067669188 +/- 0.001822436036622672</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.00413533834586467 +/- 0.0012748740569784374</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.005827067669172936 +/- 0.001315789473684198</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.0003759398496240851 +/- 0.0005869359021051138</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>-0.00028195488721804995 +/- 0.0006374370284892388</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0.012124060150375916 +/- 0.001817582669719338</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0.002349624060150357 +/- 0.001092006582577279</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>-0.00032894736842107306 +/- 0.0009172566398469527</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.0008458646616541054 +/- 0.0010465722486522654</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.0009868421052631748 +/- 0.001416805773654278</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>0.0006578947368420906 +/- 0.0008965593998279481</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.00723684210526312 +/- 0.0009208608055575914</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0.00695488721804508 +/- 0.001946646163271424</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>4.6992481202967616e-05 +/- 0.0015220051448027931</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.004417293233082664 +/- 0.0019848413610848653</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>-0.00023496240601506013 +/- 0.0006391668472150074</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-0.0007518796992481258 +/- 0.00023021520138936412</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.0023966165413533804 +/- 0.0018011060053323908</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.0038063909774436076 +/- 0.0027517699195408487</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>-4.699248120300092e-05 +/- 0.0004433261810177177</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.002913533834586479 +/- 0.0010034847981232296</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.00028195488721803884 +/- 0.0008715806856668761</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>-0.0007518796992481147 +/- 0.0009445371824361551</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-0.0013157894736841925 +/- 0.0006578947368420843</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.003289473684210531 +/- 0.0009857226016636914</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.0016917293233082776 +/- 0.00147409653584193</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>-0.0012687969924812027 +/- 0.0013132696064363028</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-9.398496240601296e-05 +/- 0.0021099571729928466</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>-0.0039003759398496206 +/- 0.0008928571428571303</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>-0.0019736842105263054 +/- 0.0010674639747744854</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.003712406015037617 +/- 0.0016203890648088758</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>-0.000610902255639112 +/- 0.0005169172932330838</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.0022556390977443554 +/- 0.0009112180183113473</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.0019266917293233154 +/- 0.0016067031012480103</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-0.01832706766917295 +/- 0.0027401089731415944</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-9.398496240601296e-05 +/- 0.0020569613372405397</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.0005639097744360888 +/- 0.0008866523620353979</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.0013157894736842146 +/- 0.0009584623145851027</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>-0.003383458646616544 +/- 0.0006578947368420954</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>-0.0023966165413533912 +/- 0.0020745996291958863</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.011419172932330812 +/- 0.0015592725585561267</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>0.002584586466165406 +/- 0.001519100552184661</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>-0.0022086466165413877 +/- 0.0021020929742805524</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>-0.000610902255639112 +/- 0.0003008986953680653</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>-0.0004229323308271082 +/- 0.000610902255639088</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>0.0012687969924811693 +/- 0.000941023702749103</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>-0.001033834586466198 +/- 0.0013748814697676496</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-0.0007048872180451359 +/- 0.0008977900927886527</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.002443609022556403 +/- 0.000958462314585082</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0012687969924811693 +/- 0.001501555010213369</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>-0.004840225563909806 +/- 0.000787737528864659</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.010667293233082653 +/- 0.0023122019925079815</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>-0.0044172932330827416 +/- 0.0019511785236867357</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>0.0009398496240601295 +/- 0.0008139336501733585</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0008458646616541166 +/- 0.0012920796132394401</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>-0.00042293233082708604 +/- 0.0004433261810177024</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0.003148496240601495 +/- 0.0021333758388752274</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>-0.005733082706766956 +/- 0.0007806977314772721</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-0.005169172932330846 +/- 0.0017708123760730127</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-0.0030545112781955154 +/- 0.001847109399157296</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-0.0018796992481203035 +/- 0.0008916196410249226</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>-0.0001409774436090361 +/- 0.000666233405956666</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>-0.004699248120300803 +/- 0.0005147768397604728</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-0.008082706766917325 +/- 0.0011851052831690365</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>0.0040413533834586235 +/- 0.0019169246291702137</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-9.398496240600184e-05 +/- 0.0006234257124728409</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.0006109022556390787 +/- 0.00141055742667328</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.0040413533834586565 +/- 0.0017857142857143004</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>-0.00014097744360902498 +/- 0.0007295194876062192</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.0014097744360902277 +/- 0.0015008194946119738</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>0.0055451127819548755 +/- 0.002109957172992822</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>0.008411654135338342 +/- 0.001550751879699258</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-0.0008928571428571507 +/- 0.0006460398066197141</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0.00042293233082709716 +/- 0.00025306225597436743</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>-0.0004229323308270527 +/- 0.0009957528242677295</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>-0.0010808270676691766 +/- 0.0008152890776737593</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>-0.0012687969924812137 +/- 0.0006322191751444358</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>-0.0018796992481202811 +/- 0.0009160521000760386</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>-0.0009398496240601406 +/- 0.0007577309913814395</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>0.0004229323308270527 +/- 0.0011404756672473324</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>-0.00023496240601506013 +/- 0.00023496240601506013</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>0.0001879699248120259 +/- 0.0008193419066805977</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>-0.0007988721804511268 +/- 0.0005580047973231974</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-0.003007518796992503 +/- 0.0010122490238974758</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>0.00277255639097741 +/- 0.0021682842095976174</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>0.001644736842105221 +/- 0.0020936719370249364</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>-0.00014097744360906938 +/- 0.0007591867679230884</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.0017857142857142683 +/- 0.001374881469767636</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-0.005968045112781972 +/- 0.001856649085069395</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>0.00032894736842102866 +/- 0.0022245865373204336</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>0.0014567669172932062 +/- 0.0009026960861042579</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>4.699248120297872e-05 +/- 0.0003289473684210414</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>-0.0015507518796992747 +/- 0.0008419395144346255</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>0.0006578947368420906 +/- 0.000703319057664274</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>-0.00042293233082708604 +/- 0.00032894736842104937</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>-0.0003759398496240962 +/- 0.0009112180183113588</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>0.0005639097744360777 +/- 0.0009112180183113427</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>0.0007988721804511156 +/- 0.0008928571428571502</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>-0.0002819548872180722 +/- 0.0002302152013894185</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0.0005169172932330546 +/- 0.000533731987387253</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>0.0007988721804511156 +/- 0.0005169172932330979</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>1.1102230246251566e-17 +/- 0.0004203135296052391</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>0.0006578947368420906 +/- 0.0011925354831249502</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>9.398496240597964e-05 +/- 0.0003516595288321236</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>4.699248120297872e-05 +/- 0.0009026960861042451</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.00018796992481200369 +/- 0.00023021520138936412</t>
+          <t>-0.000328947368421062 +/- 0.0006662334059566691</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.00046992481203009804 +/- 0.0005944130940166083</t>
+          <t>9.398496240601296e-05 +/- 0.0009112180183113428</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.00023496240601501573 +/- 0.0009913074769609595</t>
+          <t>0.0006578947368421128 +/- 0.0009208608055575892</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>-0.00028195488721806107 +/- 0.0004306932044131309</t>
+          <t>4.699248120301203e-05 +/- 0.0003289473684210842</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.0030545112781955154 +/- 0.0009687748180492583</t>
+          <t>0.0003289473684210398 +/- 0.0007877375288646795</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-0.0019266917293233154 +/- 0.0008778919968171699</t>
+          <t>0.0001879699248120259 +/- 0.0015471877474769065</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>0.00014097744360899167 +/- 0.0012263146946146506</t>
+          <t>0.0010808270676691766 +/- 0.0007295194876062004</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.001575138356747574 +/- 0.0006328679756201892</t>
+          <t>0.00046828437633037454 +/- 0.0007952976454776305</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.004257130693912303 +/- 0.0005384891715910303</t>
+          <t>0.0002554278416347699 +/- 0.0010634309064961032</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.005959982971477207 +/- 0.0012628690484624422</t>
+          <t>-0.0020008514261387724 +/- 0.000786129642938239</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.016517667092379694 +/- 0.0011068539804171909</t>
+          <t>0.011579395487441491 +/- 0.0015443471389712362</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.00051085568326944 +/- 0.0010903574691243881</t>
+          <t>0.00434227330779059 +/- 0.0009670342010728366</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.0028948488718603784 +/- 0.001472253424077523</t>
+          <t>-0.00464027245636438 +/- 0.0017495719530042206</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-8.514261387825295e-05 +/- 0.0003185744901467919</t>
+          <t>0.00038314176245209943 +/- 0.00022925350392229756</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.0001277139208174072 +/- 0.0015589470773606365</t>
+          <t>-0.0016177096636866505 +/- 0.0008471583117127485</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.003959131545338423 +/- 0.0015236722152552748</t>
+          <t>-0.0031502767134950925 +/- 0.0019985857120996976</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.00604512558535546 +/- 0.0019396825457461914</t>
+          <t>-0.0006811409110259236 +/- 0.0016835862012162836</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.004597701149425271 +/- 0.0015443471389712227</t>
+          <t>-0.0024691358024691024 +/- 0.0008032338128613472</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.0012771392081737166 +/- 0.0005711540172413304</t>
+          <t>0.0019582801191996846 +/- 0.0007422560993683733</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.0021285653469561685 +/- 0.0006864416984502677</t>
+          <t>-0.0027671349510429597 +/- 0.0007674651501626036</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0018305661983822664 +/- 0.001373543278407974</t>
+          <t>-0.006598552575564043 +/- 0.0018384693811570368</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.013409961685823734 +/- 0.0026397643248918536</t>
+          <t>0.001830566198382333 +/- 0.0014505513016092567</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.003107705406556005 +/- 0.001399683458729126</t>
+          <t>-0.0017454235845040023 +/- 0.0015519562480679515</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.002128565346956146 +/- 0.0006314345242312098</t>
+          <t>0.0036185610898254784 +/- 0.0010811771050830423</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0009791400595998145 +/- 0.0011588469637136055</t>
+          <t>-0.0008514261387824517 +/- 0.0010600169942944998</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.0005108556832694843 +/- 0.0005959982971477357</t>
+          <t>-0.00042571306939122034 +/- 0.0006864416984502677</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.00012771392081736276 +/- 0.0002725893672810784</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.003107705406556005 +/- 0.0008734901885348271</t>
+          <t>-0.0073222647935291315 +/- 0.0010736075106784712</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.003703703703703709 +/- 0.0011271351464345353</t>
+          <t>-0.008897403150276696 +/- 0.0014802331758802675</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-0.0001702852277565281 +/- 0.0007422560993683605</t>
+          <t>0.0029374201787995104 +/- 0.0009974776086726445</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.0003405704555130007 +/- 0.0008471583117127463</t>
+          <t>0.0034482758620689837 +/- 0.0007483352844294235</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.0012345679012345622 +/- 0.0008396374169142686</t>
+          <t>0.0005959982971477596 +/- 0.0009365687526607037</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>8.514261387824185e-05 +/- 0.00031857449014676515</t>
+          <t>-8.514261387824185e-05 +/- 0.00025542784163472553</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.0012345679012345512 +/- 0.0011174461258754026</t>
+          <t>-0.0003405704555129674 +/- 0.0009670342010728348</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.008386547467007233 +/- 0.0014753276671914338</t>
+          <t>0.001660280970625816 +/- 0.0016754932868586047</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.0036611323967645883 +/- 0.0009170140156891397</t>
+          <t>-0.0009791400595998035 +/- 0.000852489757109435</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.0005959982971477373 +/- 0.0012940556963448873</t>
+          <t>-0.007364836100468253 +/- 0.0016711610409868324</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0003405704555129674 +/- 0.0004964624857254161</t>
+          <t>-0.00012771392081736276 +/- 0.00019508623648172043</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.0003405704555129896 +/- 0.0003185744901468007</t>
+          <t>-0.0006811409110259348 +/- 0.0003901724729634409</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.004767986377181788 +/- 0.0013024315488104133</t>
+          <t>-0.00025542784163472553 +/- 0.0009745017575359242</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.0007237122179651223 +/- 0.001110939834031484</t>
+          <t>-0.0034482758620689503 +/- 0.0020456387870130175</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-0.00042571306939123146 +/- 0.0002692445857955415</t>
+          <t>0.0005534269902086164 +/- 0.00027258936728112695</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.000979140059599859 +/- 0.00046828437633036955</t>
+          <t>0.0 +/- 0.00038076934482753153</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.0012345679012345622 +/- 0.0006154462449894175</t>
+          <t>0.001660280970625827 +/- 0.0010154840733824103</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.003618561089825467 +/- 0.0010642826734780697</t>
+          <t>-0.0025117071094082457 +/- 0.0009020698212182643</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.2571306939120926e-05 +/- 0.0005196490257868497</t>
+          <t>0.00021285653469560462 +/- 0.00028557700862064865</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.00017028522775646148 +/- 0.0005774653029480965</t>
+          <t>-0.00021285653469560462 +/- 0.0004759616810344144</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.0017879948914431899 +/- 0.0006811409110259347</t>
+          <t>-0.0077054065559812425 +/- 0.0009974776086726363</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-0.0005534269902086386 +/- 0.0010608715022884028</t>
+          <t>-4.2571306939120926e-05 +/- 0.00040161690643065713</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.023116219667943794 +/- 0.001904322626338429</t>
+          <t>0.008684546615581112 +/- 0.0018081533062235164</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-0.013324819071945538 +/- 0.0009140447234390636</t>
+          <t>-0.014091102596849703 +/- 0.000960452462552452</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0014048531289910348 +/- 0.0006608844059710613</t>
+          <t>0.00025542784163475887 +/- 0.00047405401130951367</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.0012771392081737277 +/- 0.0005711540172413221</t>
+          <t>0.0040017028522776 +/- 0.0009170140156891543</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.0003405704555130118 +/- 0.0005317154532480707</t>
+          <t>8.514261387824185e-05 +/- 0.0003185744901467651</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.000851426138782485 +/- 0.0006595118512060413</t>
+          <t>-8.514261387823074e-05 +/- 0.000653992826553292</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.019242230736483602 +/- 0.0011549306058961841</t>
+          <t>0.00855683269476376 +/- 0.0011011083147192482</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0036611323967645657 +/- 0.0014771691420091446</t>
+          <t>0.007492550021285682 +/- 0.0013489126877611608</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.000553426990208572 +/- 0.000713625143220107</t>
+          <t>0.0023414218816518173 +/- 0.0008980427036921717</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-0.000979140059599848 +/- 0.0005727383587515561</t>
+          <t>0.00012771392081736276 +/- 0.0003324925362241919</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>-0.0002554278416347699 +/- 0.0006080398832305669</t>
+          <t>-8.514261387824185e-05 +/- 0.0003185744901467651</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>-4.2571306939120926e-05 +/- 0.00012771392081736276</t>
+          <t>0.0006385696040868583 +/- 0.0002855770086206983</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.0028097062579821364 +/- 0.0009365687526607088</t>
+          <t>0.00668369518944234 +/- 0.0010436484182317052</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.004299702000851413 +/- 0.0010331767645390705</t>
+          <t>0.0044699872286079415 +/- 0.002017089440695119</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,147 +3396,147 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-0.0008088548318433642 +/- 0.0004016169064306995</t>
+          <t>0.00012771392081737388 +/- 0.0004278363397667447</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.001532567049808442 +/- 0.00114547671750306</t>
+          <t>-0.0025968497232864763 +/- 0.0008177681018432589</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>0.003788846317581929 +/- 0.0007483352844294247</t>
+          <t>0.009110259684972376 +/- 0.001746980377069663</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>-0.00021285653469560462 +/- 0.00021285653469560464</t>
+          <t>0.0005534269902086164 +/- 0.00038314176245213516</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.002894848871860367 +/- 0.0005959982971477293</t>
+          <t>-0.006343124733929317 +/- 0.0011805384950073997</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.0036185610898254784 +/- 0.0011619705461010143</t>
+          <t>-0.002000851426138761 +/- 0.0009901833418146442</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.0019582801191996733 +/- 0.0011295444156169802</t>
+          <t>-0.010557684120902489 +/- 0.0013162728679216801</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.000893997445721606 +/- 0.0010676829462736802</t>
+          <t>-0.010004257130693871 +/- 0.0014151358142694525</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-0.00012771392081736276 +/- 0.0002725893672810784</t>
+          <t>0.00012771392081736276 +/- 0.00019508623648172046</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.008982545764154914 +/- 0.002232052231403718</t>
+          <t>0.005065985525755679 +/- 0.0009219415848321651</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.010344827586206884 +/- 0.0017454235845040268</t>
+          <t>0.003788846317581973 +/- 0.0006717638926376841</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-0.002085994040017025 +/- 0.000748335284429402</t>
+          <t>-0.0009791400595997811 +/- 0.0002725893672810784</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.006768837803320526 +/- 0.0010154840733824367</t>
+          <t>-0.004725415070242623 +/- 0.0009791400595998354</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-0.0020008514261387945 +/- 0.0008524897571094438</t>
+          <t>0.001064282673478112 +/- 0.0009754311824086362</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>0.008429118773946332 +/- 0.0018241196496916684</t>
+          <t>0.00706683695189444 +/- 0.001236767905179566</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
+          <t>0.00012771392081736276 +/- 0.00019508623648172046</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>-0.00012771392081736276 +/- 0.00019508623648172043</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>-0.00046828437633034126 +/- 0.000519649025786876</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>-0.0006811409110259903 +/- 0.0005108556832694974</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>-0.001106853980417244 +/- 0.0003405704555129896</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.0024265644955300037 +/- 0.0006035524426886813</t>
+          <t>-0.0025542784163473664 +/- 0.0003807693448275316</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-0.0011919965942954857 +/- 0.0007072476681922354</t>
+          <t>0.0019582801191996846 +/- 0.0008556726795334763</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0001702852277564837 +/- 0.00028238610390423464</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-0.000936568752660727 +/- 0.000681140911025982</t>
+          <t>0.0 +/- 0.0003807693448275316</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.002426564495530026 +/- 0.0008734901885348185</t>
+          <t>-0.0031502767134950703 +/- 0.0011133841490525288</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.0009791400595998367 +/- 0.0010083200751236274</t>
+          <t>-0.002937420178799455 +/- 0.000553426990208572</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.0012345679012346067 +/- 0.0006442207726871565</t>
+          <t>0.0020008514261388166 +/- 0.0010436484182317007</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.0018731375053214316 +/- 0.00047405401130947176</t>
+          <t>-8.514261387820854e-05 +/- 0.0008889149858587065</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.0028097062579821364 +/- 0.0013079856531065977</t>
+          <t>-0.004384844614729644 +/- 0.0010945049069546408</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.00174542358450408 +/- 0.000748335284429402</t>
+          <t>-0.002724563644103839 +/- 0.0007895801188161332</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0040877796901893524 +/- 0.0014812318827933362</t>
+          <t>0.002108433734939741 +/- 0.0011932379194373398</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,432 +3556,432 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.005507745266781416 +/- 0.0017928284557658818</t>
+          <t>0.009466437177280528 +/- 0.0015394616024094984</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0011617900172117058 +/- 0.001106278840979565</t>
+          <t>0.007099827882960386 +/- 0.0014812318827933362</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0030550774526678093 +/- 0.0011457424230373959</t>
+          <t>0.013941480206540425 +/- 0.0013359874953751993</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.002581755593803803 +/- 0.001333212855837322</t>
+          <t>0.000645438898450923 +/- 0.001493679428374328</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0016351118760757344 +/- 0.0019224017128819978</t>
+          <t>0.0032702237521514354 +/- 0.001701697068268966</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>0.0004733218588640176 +/- 0.0003012048192770805</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.004604130808950069 +/- 0.0020095171133968433</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.016092943201376907 +/- 0.002976181835764292</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.014716006884681554 +/- 0.004314957362038453</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.005895008605851959 +/- 0.002950251242069183</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.00619621342512906 +/- 0.0010919602014156315</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.004733218588640209 +/- 0.0009621635015059314</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>-0.0024096385542168863 +/- 0.002350516399956584</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0.021170395869191016 +/- 0.00282030457972013</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.003442340791738341 +/- 0.001502947435161171</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-0.001204819277108471 +/- 0.0013304324297539057</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>-0.004173838209982827 +/- 0.0009437053442109031</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.003743545611015453 +/- 0.0011713130455091318</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.00025817555938038026 +/- 0.0005163511187607513</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.005895008605851959 +/- 0.002560512142308416</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.002065404475043009 +/- 0.0006323983845395538</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>-0.0019793459552495895 +/- 0.00176577319523954</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.0005593803786574702 +/- 0.0013477159865202945</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.002108433734939741 +/- 0.0014458087449579539</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.0008175559380378394 +/- 0.0005593803786574669</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.004862306368330427 +/- 0.0011713130455091503</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.013468158347676385 +/- 0.0013749178406773075</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0.0030550774526678093 +/- 0.0013668141285945593</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.0035283993115318157 +/- 0.001344277052651738</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.0005163511187607384 +/- 0.0006024096385541974</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.0015920826161789803 +/- 0.0005788994856744344</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.014199655765920782 +/- 0.0013742443565121663</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.008950086058519758 +/- 0.00188348267024434</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>-0.00034423407917386626 +/- 0.0006024096385542244</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.000344234079173833 +/- 0.00032200149628000964</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.0022375215146299143 +/- 0.0014629948364888211</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.009079173838209952 +/- 0.002280550774526682</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.0032702237521514575 +/- 0.0010748705677105675</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.0016781411359724884 +/- 0.0008265650908906347</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.00645438898450944 +/- 0.0017318943027106637</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.000258175559380347 +/- 0.0013634233664160792</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-0.0012908777969019235 +/- 0.0013470289021083272</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.004087779690189308 +/- 0.0018281106528612828</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>-4.30292598967541e-05 +/- 0.0009117736704138287</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.008691910499139388 +/- 0.0016418919129379357</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.0001290877796901735 +/- 0.0005109441517658246</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.009466437177280528 +/- 0.0016665160697966355</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>-0.0024096385542169197 +/- 0.0016463964259646395</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-0.00012908777969021789 +/- 0.0016781411359724655</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.002667814113597211 +/- 0.0022259065673627455</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.00030120481927709 +/- 0.0006396759357710076</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>-0.000430292598967319 +/- 0.0005442818692200577</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.0002581755593803692 +/- 0.0006440029925600549</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.004905335628227159 +/- 0.0024356233559526615</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-0.00296901893287439 +/- 0.0010264079554110728</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-0.002108433734939785 +/- 0.0007804800837873063</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.00796041308089498 +/- 0.0009476211508410035</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>-0.0073580034423408325 +/- 0.001919027807313055</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.002280550774526646 +/- 0.001037174767056287</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.0010327022375214879 +/- 0.0013079762610645842</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-0.001419965576592097 +/- 0.0011553977265144288</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>0.00017211703958690537 +/- 0.0019262503688123427</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>0.004690189328743511 +/- 0.0012973161300930765</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0.0002581755593803692 +/- 0.0003442340791738163</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>-0.005851979345955283 +/- 0.0015891725742357443</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>0.0016781411359724553 +/- 0.0017044150017502813</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>-0.0005593803786575147 +/- 0.0005459801007078376</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>-0.0020223752151463325 +/- 0.0019151646372003444</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>0.001290877796901857 +/- 0.0013051420729865068</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>0.004733218588640254 +/- 0.001290877796901894</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>4.30292598967319e-05 +/- 0.0001290877796901957</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>0.0011187607573149405 +/- 0.0003943696811493645</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
           <t>-0.000430292598967319 +/- 0.0003333032139593466</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-0.0006024096385542132 +/- 0.0017233205158778836</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-0.0037005163511187543 +/- 0.00330065557844494</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.011015490533562822 +/- 0.004513767312200802</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>-0.0016351118760757344 +/- 0.0017404258533697578</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.0033993115318416535 +/- 0.0014585586279413348</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.004432013769363174 +/- 0.001478729800123889</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-0.00021514629948364837 +/- 0.0024737146904999572</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0.009982788296041312 +/- 0.0025295935381581796</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0.0011187607573149628 +/- 0.0012647967690790865</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0.0001290877796901957 +/- 0.0007709325674341133</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>-0.01024096385542168 +/- 0.001863718401695998</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>0.0001290877796901957 +/- 0.0009238773904296034</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>-4.30292598967319e-05 +/- 0.0001290877796901957</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0.000731497418244409 +/- 0.001972317837584485</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0.005206540447504304 +/- 0.0017152436685021345</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>-0.0009036144578313365 +/- 0.0008702129266848838</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>-0.0006024096385542244 +/- 0.0008209459564689766</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-0.002108433734939752 +/- 0.0010082077894887989</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.0003872633390705871 +/- 0.0003012048192771233</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>-0.0017641996557659413 +/- 0.0012829648464609098</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0.008605851979345958 +/- 0.0012471064325464236</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>-0.002022375215146299 +/- 0.0013883189160844962</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>8.60585197934638e-05 +/- 0.0010504781080665946</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>-0.0013769363166953208 +/- 0.00037512039101037544</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.0003872633390705871 +/- 0.00040593722599212864</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>0.0016351118760757344 +/- 0.0010327022375215035</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>0.0034423407917383965 +/- 0.0009427238511276534</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>-0.00043029259896730786 +/- 0.00043029259896729675</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>-0.0015060240963855388 +/- 0.0006735144510541476</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>-0.0022805507745266686 +/- 0.0011228905637435205</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>0.0026678141135972667 +/- 0.0011020867878542018</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-0.0022805507745266794 +/- 0.0005109441517658563</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.0006884681583476882 +/- 0.0013079762610646042</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.003227194492254748 +/- 0.0015060240963855546</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>-0.0002151462994836595 +/- 0.00048108175075299044</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-0.00038726333907056486 +/- 0.0014585586279413291</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>0.003485370051635106 +/- 0.0014711980204198617</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>0.0017641996557659079 +/- 0.0009318592008480332</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>-0.0006454388984509452 +/- 0.0007757210145146197</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>-0.00030120481927712326 +/- 0.00027552169696356133</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>0.0030981067125645523 +/- 0.001316442215213289</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>-0.0044320137693631525 +/- 0.0011062788409795556</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-0.006841652323580016 +/- 0.0016379403021234246</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-0.004345955249569699 +/- 0.0025416418976974588</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-0.0001721170395869276 +/- 0.00034423407917385515</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>-0.0001290877796901957 +/- 0.0003360692631629535</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0.0012048192771084265 +/- 0.0003220014962799978</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>-0.00021514629948364837 +/- 0.0016913290883849698</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-0.008820998278829595 +/- 0.0011744702292561429</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>0.001290877796901857 +/- 0.0006085256292483261</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>0.0012048192771084154 +/- 0.0019030416856708956</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>-0.0015490533562822705 +/- 0.000820945956468973</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>0.00253872633390706 +/- 0.0015804102988129965</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>-0.005335628227194478 +/- 0.0012200900928362951</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>-0.0009036144578313254 +/- 0.0009318592008479897</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-0.0009466437177280462 +/- 0.0008984773243468649</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-0.00512048192771083 +/- 0.0009896729776247882</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>0.0003012048192771011 +/- 0.000923877390429585</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-0.001376936316695332 +/- 0.0013164422152132707</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>0.0001721170395869276 +/- 0.00028542382016829285</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>-0.007487091222030973 +/- 0.001723320515877879</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>-0.008820998278829605 +/- 0.0013366802553364011</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>-0.0007314974182443867 +/- 0.0007945862871178619</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>-0.0032702237521514354 +/- 0.0011416952806731055</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>0.004475043029259907 +/- 0.0011577989713488417</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>-0.00920826161790017 +/- 0.00169078164409539</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>8.60585197934638e-05 +/- 0.0001721170395869276</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0.0001721170395869165 +/- 0.000699142719848206</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>0.000430292598967319 +/- 0.0003333032139593466</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>-0.0003442340791738552 +/- 0.000714855754123747</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>0.003098106712564541 +/- 0.0016973393221442372</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>-4.30292598967319e-05 +/- 0.0001290877796901957</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0003442340791738552 +/- 0.0005708476403365857</t>
+          <t>0.00034423407917382186 +/- 0.0005018030890572356</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.004819277108433728 +/- 0.0012589276108715705</t>
+          <t>0.0024526678141135517 +/- 0.0021171970051880383</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>-0.004518072289156627 +/- 0.0009669623517316629</t>
+          <t>-0.0030550774526678206 +/- 0.0017366984570232884</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.0002581755593803914 +/- 0.0004791535596239498</t>
+          <t>0.0005593803786574814 +/- 0.000545980100707793</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>-0.0013339070567986223 +/- 0.0008702129266848855</t>
+          <t>0.005249569707401025 +/- 0.0015370543114881093</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>-0.003829604130808939 +/- 0.0018402241635407093</t>
+          <t>0.0012048192771084154 +/- 0.0015727768401460412</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.002108433734939752 +/- 0.0015084809073113764</t>
+          <t>-0.00146299483648884 +/- 0.0011577989713488705</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.0004778453518679227 +/- 0.0011402610554653836</t>
+          <t>0.0047350130321459185 +/- 0.0010542711641626074</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0022154648132059252 +/- 0.0011888733434755841</t>
+          <t>0.001259774109469991 +/- 0.0010720210842096556</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.002867072111207658 +/- 0.0013204764685986695</t>
+          <t>0.0030842745438748654 +/- 0.0011402610554654001</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0005212858384013974 +/- 0.001225606948711197</t>
+          <t>0.0016941789748044834 +/- 0.001522897319110174</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.001563857515204159 +/- 0.001376453476781485</t>
+          <t>0.0003909643788010175 +/- 0.0010362172408233277</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.002953953084274563 +/- 0.0009276349480478991</t>
+          <t>0.004474370112945237 +/- 0.0019911670958063926</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.00017376194613381025 +/- 0.00028815158908389733</t>
+          <t>0.0002172024326672184 +/- 0.0002914076425933427</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0011728931364031526 +/- 0.0009527242484561864</t>
+          <t>0.0023892267593396688 +/- 0.0005908544964698334</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.027801911381407494 +/- 0.002371389064110558</t>
+          <t>0.014509122502171989 +/- 0.0027964338730549253</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.02415291051259777 +/- 0.003842457756298171</t>
+          <t>0.013423110338835753 +/- 0.0028249679388165166</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.006081668114682881 +/- 0.0016824428089519644</t>
+          <t>0.005777584708948702 +/- 0.001374395483888473</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-0.000434404865334459 +/- 0.0011160063057050508</t>
+          <t>0.002215464813205892 +/- 0.0010894818595989964</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-0.004691572545612499 +/- 0.001527228134773831</t>
+          <t>-0.0006950477845352298 +/- 0.0006785620917381766</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0034752389226759715 +/- 0.002606429192006948</t>
+          <t>-0.0016072980017376559 +/- 0.0026852405665552794</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.016637706342311043 +/- 0.003227777235145093</t>
+          <t>0.016029539530842695 +/- 0.0022273577312414052</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.008384013900955712 +/- 0.001671753380095019</t>
+          <t>0.003649000868809693 +/- 0.0011361161451452686</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.0006950477845352077 +/- 0.0011361161451452866</t>
+          <t>0.0035186794092093576 +/- 0.0011566921768631155</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.0031277150304083513 +/- 0.001370958630587288</t>
+          <t>0.00026064291920065987 +/- 0.001306107417756097</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.005169417897480477 +/- 0.0007879390593925902</t>
+          <t>0.004821894005212823 +/- 0.001393485224356685</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.0002606429192007154 +/- 0.00028815158908389733</t>
+          <t>-0.0004344048653345256 +/- 0.0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.0037358818418766425 +/- 0.0013764534767814842</t>
+          <t>0.005994787141615931 +/- 0.0009477595234262189</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.0038662033014770004 +/- 0.0009606144390745501</t>
+          <t>0.0036924413553431567 +/- 0.0009762035210358021</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-0.002041702867072115 +/- 0.0011825071753966971</t>
+          <t>-0.0003475238922676205 +/- 0.0006673454168434803</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-4.3440486533441455e-05 +/- 0.001123589674750442</t>
+          <t>-0.0007384882710686713 +/- 0.0006158751902153589</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.001737619461337958 +/- 0.0010094656853711892</t>
+          <t>-0.003605560382276318 +/- 0.0016941789748045148</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.000390964378801073 +/- 0.00045353199430544583</t>
+          <t>0.0003040834057341013 +/- 0.00027815483220817685</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-0.00013032145960033547 +/- 0.0015907761445352424</t>
+          <t>-0.003605560382276318 +/- 0.0016830035297837093</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.002128583840139009 +/- 0.00164214232592839</t>
+          <t>-0.0031277150304083847 +/- 0.0015758781187851473</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.0020851433536056008 +/- 0.0011460387452886986</t>
+          <t>0.0019548218940051653 +/- 0.0013068296226317344</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0019982623805386733 +/- 0.0016958489396996677</t>
+          <t>0.003692441355343146 +/- 0.001604948149601309</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-0.0004344048653344923 +/- 0.0003364885617903757</t>
+          <t>0.0006516072980016884 +/- 0.00048567940432226597</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.001042571676802817 +/- 0.0004430077770280305</t>
+          <t>0.00021720243266719618 +/- 0.0002914076425933427</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.0027367506516073115 +/- 0.0011336219244743697</t>
+          <t>0.003909643788010397 +/- 0.001780530107030331</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.003171155516941815 +/- 0.0011664397551778768</t>
+          <t>-0.006646394439617764 +/- 0.000847924469849835</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00038854352345785647</t>
+          <t>-0.0003475238922676205 +/- 0.00032507883464589344</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.0014769765421372872 +/- 0.0008512562094815693</t>
+          <t>0.00039096437880099534 +/- 0.0005302587148450768</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.00356211989574281 +/- 0.0014116487236552414</t>
+          <t>-0.000868809730669029 +/- 0.0012286825042337822</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.00017376194613381025 +/- 0.0009752365039376158</t>
+          <t>0.0037358818418765983 +/- 0.0018348142555988697</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0009122502172024593 +/- 0.0010362172408233457</t>
+          <t>0.00026064291920064876 +/- 0.00052128583840139</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.0008253692441355543 +/- 0.0014335360556038254</t>
+          <t>-0.001520417028670762 +/- 0.0009163780673209869</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.004865334491746332 +/- 0.0013571241834764206</t>
+          <t>0.005603822762814892 +/- 0.0013382208341224308</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-0.0004344048653344701 +/- 0.00141431977377061</t>
+          <t>0.00299739357080796 +/- 0.0008997530485320618</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.0017376194613380135 +/- 0.0009517333753347735</t>
+          <t>-0.0006516072980017662 +/- 0.0015572066315321241</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.003344917463075603 +/- 0.001289385063393217</t>
+          <t>0.00299739357080796 +/- 0.0013382208341224308</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0025629887054735125 +/- 0.0009407648926023977</t>
+          <t>-0.00026064291920074867 +/- 0.0007058243618276128</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.00047784535186796707 +/- 0.0016535939453235758</t>
+          <t>8.688097306687181e-05 +/- 0.001129452649869701</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.0003040834057341679 +/- 0.00033928104586912526</t>
+          <t>8.688097306686071e-05 +/- 0.0003250788346458459</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>-4.3440486533430356e-05 +/- 0.0011888733434755874</t>
+          <t>0.0009991311902692868 +/- 0.001166439755177882</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>8.688097306689402e-05 +/- 0.0007722149797841571</t>
+          <t>0.0017376194613379248 +/- 0.001317615194448579</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.003127715030408362 +/- 0.0013147476933467973</t>
+          <t>0.004648132059079035 +/- 0.0011664397551778873</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0006950477845352077 +/- 0.0009357367171389335</t>
+          <t>0.006993918331885262 +/- 0.0015474815925766185</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>0.0002172024326672628 +/- 0.0002914076425933923</t>
+          <t>0.0006950477845351522 +/- 0.00044300777702804356</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>-0.00013032145960034658 +/- 0.0003392810458691011</t>
+          <t>0.00034752389226754276 +/- 0.00026064291920067093</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>-0.0009122502172024483 +/- 0.0006280118286186333</t>
+          <t>-8.688097306691622e-05 +/- 0.00026064291920069316</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.0035186794092093797 +/- 0.0005647263249348363</t>
+          <t>0.012119895742832298 +/- 0.0021054076135625707</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0038227628149435366 +/- 0.0009070639886108428</t>
+          <t>0.002302345786272764 +/- 0.000869895064921848</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,92 +4286,92 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0002172024326672406 +/- 0.00048567940432229075</t>
+          <t>0.00017376194613376582 +/- 0.0003475238922675733</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0.005082536924413583 +/- 0.0014544456162279109</t>
+          <t>0.0032580364900086423 +/- 0.0012325161563085238</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>0.008861859252823633 +/- 0.0010131975490608707</t>
+          <t>0.002649869678540373 +/- 0.0018679409209383182</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>-4.344048653345256e-05 +/- 0.0003608437820555483</t>
+          <t>0.00017376194613375474 +/- 0.0004837327856498594</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.0017376194613379803 +/- 0.00067297712358078</t>
+          <t>0.0050825369244135166 +/- 0.0011825071753966828</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.004039965247610811 +/- 0.0011501478970350966</t>
+          <t>0.0067332754126845805 +/- 0.0012015044905246983</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0.009556907037358831 +/- 0.000990595503995785</t>
+          <t>0.002953953084274519 +/- 0.0013431472488045321</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-0.002215464813205903 +/- 0.0008115352603070939</t>
+          <t>-0.00026064291920072644 +/- 0.000781928757602093</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0.000695047784535241 +/- 0.00028815158908389733</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.00034752389226758715 +/- 0.0013431472488045536</t>
+          <t>0.0017376194613379248 +/- 0.0005494835204462856</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>-0.002649869678540373 +/- 0.0007879390593925809</t>
+          <t>-0.0001303214596004021 +/- 0.0008021800743970146</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.00030408340573414574 +/- 0.0003392810458690883</t>
+          <t>0.00039096437880099534 +/- 0.0004098167303239069</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.0025195482189400266 +/- 0.0008423422862582529</t>
+          <t>0.0005212858384013419 +/- 0.0017245380748287748</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.0011294526498696667 +/- 0.0009357367171389211</t>
+          <t>0.0008253692441354988 +/- 0.0007879390593925809</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0.0012597741094700465 +/- 0.00130971445974642</t>
+          <t>0.0005647263249347944 +/- 0.000390964378801041</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>4.344048653345256e-05 +/- 0.00013032145960035766</t>
+          <t>-1.1102230246251566e-17 +/- 0.00019427176172890343</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-4.344048653345256e-05 +/- 0.0003040834057341679</t>
+          <t>0.00013032145960032438 +/- 0.00019906931776520533</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00038854352345785647</t>
+          <t>8.688097306686071e-05 +/- 0.0004256281047407637</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-4.344048653345256e-05 +/- 0.0003040834057341679</t>
+          <t>-0.00017376194613382133 +/- 0.0002881515890838739</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.0015204170286707175 +/- 0.0009367445114182358</t>
+          <t>-0.0028236316246742386 +/- 0.0010860121633362474</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4396,37 +4396,37 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.00047784535186795596 +/- 0.0005972079532957297</t>
+          <t>0.00026064291920064876 +/- 0.0003475238922675733</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.0009556907037358786 +/- 0.00104257167680278</t>
+          <t>0.0017376194613379248 +/- 0.0006729771235807944</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>-0.0011728931364031081 +/- 0.001133621924474368</t>
+          <t>0.0016072980017375782 +/- 0.0012447044988613868</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0.0005212858384014196 +/- 0.0003787053817150955</t>
+          <t>4.3440486533430356e-05 +/- 0.00023393417928471198</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.00026064291920072644 +/- 0.001049786791797993</t>
+          <t>0.0005212858384013419 +/- 0.0006950477845351827</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.0006081668114683136 +/- 0.0005563096644164143</t>
+          <t>-0.0008253692441355764 +/- 0.0014596262047273066</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.0013900955690704041 +/- 0.0008423422862582666</t>
+          <t>-4.344048653348587e-05 +/- 0.0008344644966246108</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.0018198786747550156 +/- 0.0008963776347316163</t>
+          <t>-0.009659356042930467 +/- 0.0009344369759449734</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,432 +4446,432 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.0031264582361175907 +/- 0.0016305557825157387</t>
+          <t>-0.008866075594960332 +/- 0.0011430190120313474</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0058329444703686395 +/- 0.0012213021304995236</t>
+          <t>-0.006019598693420436 +/- 0.001113099434612838</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.005739617358842741 +/- 0.0012177310639943893</t>
+          <t>-0.0006532897806812877 +/- 0.002908154260547434</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.006952869808679418 +/- 0.0019063647424932791</t>
+          <t>-0.009799346710219314 +/- 0.0021179292053962132</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.0065795613625758255 +/- 0.0017011410297301144</t>
+          <t>-0.005226318245450301 +/- 0.002226198869225676</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.00041997200186654203 +/- 0.0002512909382703921</t>
+          <t>-0.0002799813345776947 +/- 0.00030953101169905724</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.0074661689220718586 +/- 0.001043428827578063</t>
+          <t>-0.007279514699020062 +/- 0.001564447467497919</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.010779281381241245 +/- 0.0030560176070990076</t>
+          <t>0.008726084927671485 +/- 0.0028079675937154225</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.007699486700886604 +/- 0.0022979136261773447</t>
+          <t>0.0033597760149323363 +/- 0.0027511718101696065</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.003919738684087726 +/- 0.0021606788432646236</t>
+          <t>0.012039197386840872 +/- 0.0019217228447945863</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.0034064395706952856 +/- 0.0007822237337489595</t>
+          <t>-0.002799813345776947 +/- 0.0011805049594655634</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.003219785347643489 +/- 0.0018246584037346842</t>
+          <t>-0.011199253383107788 +/- 0.001770757439198345</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.0050863275781614535 +/- 0.0014222819089247003</t>
+          <t>0.020345310312645814 +/- 0.002616490110849497</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-0.022351843210452627 +/- 0.003653193191983168</t>
+          <t>-0.002006532897806812 +/- 0.0025046639104656346</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.00013999066728884735 +/- 0.0017341021162913708</t>
+          <t>0.003079794680354642 +/- 0.001659019023297356</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.004386374241717217 +/- 0.0014184492910471916</t>
+          <t>-0.006392907139524029 +/- 0.001416144741529959</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.010219318712085857 +/- 0.002299808031796846</t>
+          <t>-0.003639757349510031 +/- 0.0016137766183658957</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.002706486234251049 +/- 0.0006858114072188083</t>
+          <t>-0.002379841343910405 +/- 0.0006746071999440482</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.0005132991133924402 +/- 0.00013999066728884735</t>
+          <t>-4.666355576294911e-05 +/- 0.0002512909382703921</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.009986000933271112 +/- 0.0021505774375740376</t>
+          <t>-0.009799346710219314 +/- 0.002228154248495253</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.0074661689220718586 +/- 0.001656391913140349</t>
+          <t>0.004153056462902471 +/- 0.002365156490429152</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.003919738684087726 +/- 0.0011276757791502162</t>
+          <t>0.0018198786747550156 +/- 0.0007653392191720353</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.332711152589823e-05 +/- 0.000829509511648678</t>
+          <t>0.0019132057862809137 +/- 0.0010933620638226764</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.0009332711152589823 +/- 0.0008853787195991725</t>
+          <t>-0.0010265982267848805 +/- 0.000829509511648678</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.00018665422305179645 +/- 0.0005196233656397591</t>
+          <t>9.332711152589823e-05 +/- 0.0005828276246755386</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.0005132991133924402 +/- 0.0012069544709638412</t>
+          <t>0.010452636490900603 +/- 0.001478579516356029</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.00578628091460569 +/- 0.001605660339158679</t>
+          <t>0.01213252449836677 +/- 0.0020446945683813937</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.006019598693420436 +/- 0.001739117606494094</t>
+          <t>0.00368642090527298 +/- 0.0013435539009694786</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.00895940270648623 +/- 0.0015588700969192777</t>
+          <t>0.0010265982267848805 +/- 0.0023683765824450797</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.0008399440037330841 +/- 0.0004068034478339404</t>
+          <t>-0.0006066262249183385 +/- 0.0006937036279663322</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
+          <t>-0.0009332711152589823 +/- 0.0005111736420953484</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0.00634624358376108 +/- 0.002982089651641708</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0.0017265515632291172 +/- 0.001643855805301776</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>0.0002799813345776947 +/- 0.0005196233656397591</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>0.0026131591227251507 +/- 0.0009379258629137551</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>0.007186187587494164 +/- 0.0012555878718687543</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0.005319645356976199 +/- 0.0011468227463783949</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.0005599626691553894 +/- 0.001213252449836677</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.004619692020531962 +/- 0.002142970135922544</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.0008399440037330841 +/- 0.002084769753027407</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>-0.0019132057862809137 +/- 0.0012248627856655792</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.009612692487167517 +/- 0.0021505774375740376</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>-0.007046196920205317 +/- 0.002271226042676239</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.0031264582361175907 +/- 0.0013532431171255244</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0014932337844143716 +/- 0.0009964608727980686</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>9.332711152589823e-05 +/- 0.0005441858977923749</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>-0.000793280447970135 +/- 0.0013206693138669995</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.012925804946336905 +/- 0.0015623582867739802</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-0.00891273915072328 +/- 0.0016225234391706676</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>0.009659356042930467 +/- 0.001252983815408077</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-0.0008399440037330841 +/- 0.0010803394216323118</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>-0.0005599626691553894 +/- 0.0006532897806812876</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>-0.0002799813345776947 +/- 0.0007581930382301406</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>-0.009146056929538026 +/- 0.0014337182917160253</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>0.014512365842277174 +/- 0.00235593197598961</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-0.00023331777881474558 +/- 0.0005619036201023</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>9.332711152589823e-05 +/- 0.0011003104174103211</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>0.004106392907139522 +/- 0.002084769753027407</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.00158656089594027 +/- 0.0005975850898210775</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>-0.0073261782547830116 +/- 0.0012177310639943895</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-0.007886140923938401 +/- 0.0022903203344485337</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-0.0021465235650956595 +/- 0.0023350435843577785</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>0.0013065795613625753 +/- 0.001600226616843886</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0.00023331777881474558 +/- 0.00023331777881474558</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>-0.00475968268782081 +/- 0.001213252449836677</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>0.0002799813345776947 +/- 0.0010475942286814577</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0.002379841343910405 +/- 0.0010527778042630398</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0.00032664489034064383 +/- 0.0021490581315295287</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>-0.0002799813345776947 +/- 0.0017854527736545947</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>0.003219785347643489 +/- 0.0018483716584543493</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
           <t>-0.00032664489034064383 +/- 0.00029879254491053876</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>-0.0011199253383107788 +/- 0.0006664888874048388</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>0.0003733084461035929 +/- 0.0004068034478339404</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-0.003639757349510031 +/- 0.0015727764392303042</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>0.004526364909006065 +/- 0.001617146379016654</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>-0.00032664489034064383 +/- 0.00029879254491053876</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>-0.001166588894073728 +/- 0.000730400179304644</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>-0.0013065795613625753 +/- 0.0011392025772966586</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0.002799813345776947 +/- 0.0012346016383875825</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-0.00018665422305179645 +/- 0.0010475942286814577</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.0022398506766215577 +/- 0.0012486316528473773</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.006019598693420436 +/- 0.001553973476933897</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>-0.0049463369108726065 +/- 0.0013394960424085226</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-0.0030331311245916925 +/- 0.002015195789238374</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>-0.012085860942603822 +/- 0.00217323957483808</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>0.004573028464769013 +/- 0.0011392025772966588</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>-0.013905739617358836 +/- 0.002897652766450773</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.00020868576551561255</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.0038264115725618274 +/- 0.0013811151271067416</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.000793280447970135 +/- 0.0018198786747550156</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-0.014885674288380769 +/- 0.0027084968475840306</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-0.010405972935137653 +/- 0.0019912821552358242</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>0.00023331777881474558 +/- 0.0005994042267225909</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>-0.0007466168922071858 +/- 0.0005975850898210775</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0.0005599626691553894 +/- 0.0008804462092446663</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>-0.002706486234251049 +/- 0.0017682963435834257</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-0.008306112925804942 +/- 0.002687107801938957</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0005902524797327817</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>-0.004573028464769013 +/- 0.0011199253383107788</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-0.0010732617825478298 +/- 0.0005540990241268274</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>0.0025664955669622014 +/- 0.0015789943365085042</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>0.009239384041063925 +/- 0.0019442526043863416</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>-0.0006066262249183385 +/- 0.0008866075594960332</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-0.0034064395706952856 +/- 0.0015055777699394934</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-0.010172655156322907 +/- 0.002571157688092563</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-0.01059262715818945 +/- 0.0021081394303455927</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>9.332711152589823e-05 +/- 0.0014122954690080772</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>-9.332711152589823e-05 +/- 0.00018665422305179645</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0.003079794680354642 +/- 0.0012024357187797592</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0.0002799813345776947 +/- 0.000937925862913755</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>-0.000793280447970135 +/- 0.0008095824345729102</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>-0.004899673355109657 +/- 0.00284035049809299</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>-0.002426504899673354 +/- 0.0016405409081891682</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>-0.004899673355109657 +/- 0.0026252138458301814</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0003614543486894461</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>0.001166588894073728 +/- 0.0010691963823975356</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>-0.00013999066728884735 +/- 0.0005132991133924402</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>-9.332711152589823e-05 +/- 0.00018665422305179645</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>-0.0025664955669622014 +/- 0.0011477717103358692</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>-0.00013999066728884735 +/- 0.00021383927647950716</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>-0.001259916005599626 +/- 0.0005920941456112699</t>
+          <t>-0.0006532897806812877 +/- 0.0008136068956678808</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.008679421371908535 +/- 0.0016979379746766444</t>
+          <t>0.003593093793747082 +/- 0.001708803865944988</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>-0.0013065795613625753 +/- 0.001195170179642155</t>
+          <t>-0.0043397106859542674 +/- 0.0012177310639943893</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>0.0014932337844143716 +/- 0.0005828276246755386</t>
+          <t>0.001633224451703219 +/- 0.0010486329936651528</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.0003733084461035929 +/- 0.0014428021310070275</t>
+          <t>-0.0014465702286514226 +/- 0.0018126854502617847</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>-0.009286047596826875 +/- 0.0030560176070990076</t>
+          <t>-0.0038730751283247767 +/- 0.0015342307254105076</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.0014465702286514226 +/- 0.0006746071999440482</t>
+          <t>0.0006532897806812877 +/- 0.0014932337844143718</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.0034793814432989567 +/- 0.0019157305086750583</t>
+          <t>-0.007474226804123685 +/- 0.001979676739141387</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.027276632302405422 +/- 0.0017840686990803736</t>
+          <t>-0.022551546391752563 +/- 0.0026911434892916246</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.0018470790378006807 +/- 0.000999115408042351</t>
+          <t>0.0004725085910652904 +/- 0.0015659558533984638</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.002448453608247414 +/- 0.000816151202749138</t>
+          <t>-0.0002577319587628857 +/- 0.0015150508667137745</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.009149484536082442 +/- 0.001137302602652378</t>
+          <t>-0.002319587628865971 +/- 0.002158050977161585</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.005927835051546371 +/- 0.002012950947398615</t>
+          <t>-0.0060567010309278135 +/- 0.0026856527546976856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.00030068728522336663 +/- 0.0002750482919859461</t>
+          <t>-0.0003865979381443285 +/- 0.00012886597938144284</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.0034364261168384758 +/- 0.0017606444615050794</t>
+          <t>0.003092783505154628 +/- 0.002604382541447434</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-0.0018900343642611506 +/- 0.00358464708677407</t>
+          <t>0.002534364261168376 +/- 0.0033463825951137887</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.00455326460481098 +/- 0.0034960463830542494</t>
+          <t>-0.011941580756013703 +/- 0.004716487021068988</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-0.004682130584192423 +/- 0.0017443247855882201</t>
+          <t>-0.0006872852233676952 +/- 0.001834549527840425</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.0028780068728522235 +/- 0.001303607466107686</t>
+          <t>-0.008075601374570418 +/- 0.0019571796821124528</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-0.0029639175257731853 +/- 0.0015541282229489242</t>
+          <t>-0.009364261168384846 +/- 0.0021546282137430255</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>-0.016494845360824684 +/- 0.003372471894568806</t>
+          <t>-0.010567010309278313 +/- 0.004287793715968294</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.004080756013745757 +/- 0.0039051565896278504</t>
+          <t>0.013530927835051599 +/- 0.002461981079193673</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>-0.0036512027491408805 +/- 0.0009653009043919309</t>
+          <t>-0.0012886597938144284 +/- 0.001560644512421382</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.005841924398625409 +/- 0.0022501376037300253</t>
+          <t>-0.008891752577319556 +/- 0.002655250766413322</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-0.001675257731958757 +/- 0.001127526181134591</t>
+          <t>0.0029209621993127044 +/- 0.0016502897519156767</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.006958762886597913 +/- 0.002049288735717615</t>
+          <t>-0.001546391752577314 +/- 0.002642363659661451</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00021477663230240474 +/- 0.00034631691358670623</t>
+          <t>0.0006872852233676952 +/- 0.0003936920700133869</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.0027491408934708474 +/- 0.001574768280053592</t>
+          <t>-0.003135738831615109 +/- 0.0016418827193828457</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.00678694158075599 +/- 0.0010309278350515427</t>
+          <t>-0.006701030927835028 +/- 0.0010018817688737592</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.001589347079037806 +/- 0.0006939645370018823</t>
+          <t>0.002577319587628857 +/- 0.001524762830695772</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0010738831615120458 +/- 0.001233797819273662</t>
+          <t>0.0030498281786941472 +/- 0.0020730117718236445</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.00030068728522336663 +/- 0.0012604296177939139</t>
+          <t>0.0004725085910652904 +/- 0.0013092569290488072</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.00012886597938144284 +/- 0.000608996859053169</t>
+          <t>-0.0005154639175257714 +/- 0.0010661231654631282</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.001632302405498298 +/- 0.0015700744744413548</t>
+          <t>0.003135738831615109 +/- 0.001664207098609145</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-0.029896907216494805 +/- 0.0022087560364575003</t>
+          <t>-0.027878006872852246 +/- 0.0020730117718236445</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.01361683848797246 +/- 0.0014382018077992392</t>
+          <t>-0.012585910652920917 +/- 0.003393470790377995</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.004596219931271461 +/- 0.0014636361715980035</t>
+          <t>0.0036941580756013614 +/- 0.002330697588702833</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-0.0005584192439862523 +/- 0.0005779048130186281</t>
+          <t>-0.00030068728522336663 +/- 0.0005450419905691355</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.002061855670103119 +/- 0.0006313117893771478</t>
+          <t>-0.0003436426116838476 +/- 0.00037447585425607027</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.006271477663230218 +/- 0.0017096004073996847</t>
+          <t>-0.0035223367697594377 +/- 0.0016049434443530359</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.017525773195876226 +/- 0.00270857092275505</t>
+          <t>-0.02452749140893471 +/- 0.0027061855670103335</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.00021477663230240474 +/- 0.00034631691358670623</t>
+          <t>0.0018041237113401998 +/- 0.0004208745262514037</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.0002577319587628857 +/- 0.000613524779084435</t>
+          <t>0.0005584192439862523 +/- 0.0010174157459043787</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.0005584192439862523 +/- 0.0011693004801388446</t>
+          <t>-0.0012457044673539475 +/- 0.0023088238230887697</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>-0.004682130584192423 +/- 0.0010943074916543772</t>
+          <t>-0.008204467353951861 +/- 0.0020189003436426045</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.004037800687285209 +/- 0.00047833027172079057</t>
+          <t>-4.295532646048095e-05 +/- 0.0010064754736993076</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.0007302405498281761 +/- 0.0012457044673539475</t>
+          <t>0.000816151202749138 +/- 0.001060048340142012</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.010137457044673504 +/- 0.0009832923661735014</t>
+          <t>-0.006271477663230218 +/- 0.001864478901564487</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0017182130584192713 +/- 0.0011841966281864772</t>
+          <t>-0.0026202749140893378 +/- 0.001175595548402402</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.016967353951889974 +/- 0.002007903074316186</t>
+          <t>-0.02156357388316149 +/- 0.002188614983308805</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>-0.0012457044673539475 +/- 0.0009498859272979339</t>
+          <t>-0.001675257731958757 +/- 0.0016796576285238044</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0005584192439862523 +/- 0.000999115408042351</t>
+          <t>-0.0009879725085910618 +/- 0.0015253677753062406</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.001675257731958757 +/- 0.0014175257731958713</t>
+          <t>-0.00317869415807559 +/- 0.001998230816084702</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>8.59106529209619e-05 +/- 0.0002577319587628857</t>
+          <t>-0.0006443298969072142 +/- 0.0007501825256259844</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-0.0038659793814432852 +/- 0.0008373534660488771</t>
+          <t>0.0073024054982817835 +/- 0.0017289185393039909</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-0.004381443298969057 +/- 0.0011168384879725046</t>
+          <t>0.0 +/- 0.0015368164793812934</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.005756013745704447 +/- 0.0017096004073996847</t>
+          <t>-0.02109106529209619 +/- 0.0020370971995497572</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.001546391752577314 +/- 0.0019796767391413866</t>
+          <t>-0.00678694158075599 +/- 0.0017585472070840763</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>0.00012886597938144284 +/- 0.0005450419905691355</t>
+          <t>-0.0005154639175257714 +/- 0.0006013745704467333</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.0002577319587628857 +/- 0.0005154639175257714</t>
+          <t>-0.0026202749140893378 +/- 0.0008024717221765178</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0009879725085910618 +/- 0.000608996859053169</t>
+          <t>-0.0003865979381443285 +/- 0.000405239739349509</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.010352233676975908 +/- 0.0020461349422361704</t>
+          <t>-0.0038230240549828043 +/- 0.002637121216180545</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.004939862542955309 +/- 0.0009653009043919309</t>
+          <t>-0.0027491408934707806 +/- 0.002908300838455446</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,92 +5176,92 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.0006013745704467333 +/- 0.0008195353964063079</t>
+          <t>0.0006013745704467333 +/- 0.0007489517085121405</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>0.003135738831615198 +/- 0.0009420838573652065</t>
+          <t>-0.0052835051546391565 +/- 0.0014636361715980035</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-0.01451890034364256 +/- 0.0013141802870084449</t>
+          <t>-0.005025773195876271 +/- 0.0024754346278735148</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>-0.0005584192439862523 +/- 0.0006385768362250194</t>
+          <t>-0.007087628865979356 +/- 0.0014279012146558938</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-0.0014175257731958713 +/- 0.0007452470606914695</t>
+          <t>-0.007388316151202723 +/- 0.0007873841400267738</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.010481099656357351 +/- 0.0011068813339110894</t>
+          <t>-0.017525773195876237 +/- 0.002049288735717641</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-0.0012027491408934665 +/- 0.00139588288739449</t>
+          <t>0.0045103092783504994 +/- 0.0013752414599297307</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.002963917525773252 +/- 0.0013371462556936297</t>
+          <t>0.003393470790377995 +/- 0.0009691163378589723</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>0.0001718213058419238 +/- 0.0002849334012332807</t>
+          <t>-4.295532646048095e-05 +/- 0.00030068728522336663</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.0031786941580756343 +/- 0.0013610807145837999</t>
+          <t>-0.01039518900343639 +/- 0.0011965969310295593</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.0005154639175257714 +/- 0.0011168384879725046</t>
+          <t>4.295532646048095e-05 +/- 0.001404448687652213</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-0.0014175257731958713 +/- 0.0005450419905691355</t>
+          <t>0.0028780068728522235 +/- 0.0009420838573651732</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.00584192439862552 +/- 0.001073023711065013</t>
+          <t>-0.00408075601374569 +/- 0.002097786159291192</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.006701030927835028 +/- 0.0011234275627682107</t>
+          <t>0.0006443298969072142 +/- 0.0011405427875731708</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.005584192439862634 +/- 0.001184196628186441</t>
+          <t>-0.0014175257731958713 +/- 0.0017294520738142033</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>-0.00042955326460480947 +/- 0.0</t>
+          <t>-4.295532646048095e-05 +/- 0.00023132151233395552</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>-4.295532646048095e-05 +/- 0.00023132151233395552</t>
+          <t>-0.0006443298969072142 +/- 0.0011405427875731706</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.0009450171821305808 +/- 0.0004208745262514037</t>
+          <t>0.00030068728522336663 +/- 0.0013991836318644564</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,52 +5271,52 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-0.0003436426116838476 +/- 0.0005365118555325065</t>
+          <t>-0.00042955326460480947 +/- 0.0008373534660488771</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.0050687285223368515 +/- 0.0015463917525773351</t>
+          <t>-0.00012886597938144284 +/- 0.001771614315060241</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0.0011597938144329856 +/- 0.0002750482919859461</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0008591065292096189 +/- 0.0004705520253480792</t>
+          <t>0.0018900343642611617 +/- 0.001217993718106338</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.0005584192439862523 +/- 0.0011534125070530503</t>
+          <t>0.0004725085910652904 +/- 0.001565955853398464</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>-0.004166666666666652 +/- 0.00138593348839361</t>
+          <t>-0.003994845360824728 +/- 0.0006939645370018666</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.0012457044673539585 +/- 0.0008024717221765364</t>
+          <t>0.0006013745704467333 +/- 0.0007489517085121405</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.0012027491408934665 +/- 0.001672501918722656</t>
+          <t>0.008376288659793818 +/- 0.0018748413095185201</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-0.0014604810996563522 +/- 0.0015392158820591798</t>
+          <t>0.007259450171821303 +/- 0.002055132940533646</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.0024484536082474582 +/- 0.0012749847147471055</t>
+          <t>0.0060996563573882945 +/- 0.0015934052397758884</t>
         </is>
       </c>
     </row>
